--- a/backend/processing/fixtures/processing_templates.xlsx
+++ b/backend/processing/fixtures/processing_templates.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7134,7 +7134,7 @@
         </is>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="99" customHeight="1">
       <c r="A166" s="4" t="n">
         <v>165</v>
       </c>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="73" customHeight="1">
       <c r="A167" s="4" t="n">
         <v>166</v>
       </c>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="73" customHeight="1">
       <c r="A168" s="4" t="n">
         <v>167</v>
       </c>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="60" customHeight="1">
       <c r="A169" s="4" t="n">
         <v>168</v>
       </c>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="73" customHeight="1">
       <c r="A170" s="4" t="n">
         <v>169</v>
       </c>
@@ -7334,7 +7334,7 @@
         </is>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="73" customHeight="1">
       <c r="A171" s="4" t="n">
         <v>170</v>
       </c>
@@ -7374,7 +7374,7 @@
         </is>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="86" customHeight="1">
       <c r="A172" s="4" t="n">
         <v>171</v>
       </c>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="99" customHeight="1">
       <c r="A173" s="4" t="n">
         <v>172</v>
       </c>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="45" customHeight="1">
       <c r="A174" s="4" t="n">
         <v>173</v>
       </c>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="112" customHeight="1">
       <c r="A175" s="4" t="n">
         <v>174</v>
       </c>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="47" customHeight="1">
       <c r="A176" s="4" t="n">
         <v>175</v>
       </c>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="112" customHeight="1">
       <c r="A177" s="4" t="n">
         <v>176</v>
       </c>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="151" customHeight="1">
       <c r="A178" s="4" t="n">
         <v>177</v>
       </c>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
     </row>
-    <row r="179">
+    <row r="179" ht="216" customHeight="1">
       <c r="A179" s="4" t="n">
         <v>178</v>
       </c>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="151" customHeight="1">
       <c r="A180" s="4" t="n">
         <v>179</v>
       </c>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="164" customHeight="1">
       <c r="A181" s="4" t="n">
         <v>180</v>
       </c>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="138" customHeight="1">
       <c r="A182" s="4" t="n">
         <v>181</v>
       </c>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="112" customHeight="1">
       <c r="A183" s="4" t="n">
         <v>182</v>
       </c>
@@ -7854,7 +7854,7 @@
         </is>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="99" customHeight="1">
       <c r="A184" s="4" t="n">
         <v>183</v>
       </c>
@@ -7894,7 +7894,7 @@
         </is>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="138" customHeight="1">
       <c r="A185" s="4" t="n">
         <v>184</v>
       </c>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="47" customHeight="1">
       <c r="A186" s="4" t="n">
         <v>185</v>
       </c>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="86" customHeight="1">
       <c r="A187" s="4" t="n">
         <v>186</v>
       </c>
@@ -8009,6 +8009,2246 @@
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="47" customHeight="1">
+      <c r="A188" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>أشغال عمومية / Travaux publics</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>إدارة حضور العمال / Gestion de la présence des travailleurs</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>متابعة ومراقبة حضور العمال / Suivi et contrôle de la présence des travailleurs</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>تسيير حضور الموظفين / Gestion de la présence des employés</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، المتمهنون / Salariés, apprentis</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، الوظيفة، رقم التسجيل / Nom et prénom, fonction, matricule</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>36 شهر (03 سنوات) / 36 mois (3 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="99" customHeight="1">
+      <c r="A189" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>أشغال عمومية / Travaux publics</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>طب العمل / Médecine du travail</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>مراقبة الحالة الصحية للعمال والمتمهنين عن طريق إجراء فحوص طبية دورية وإجراء تقييم الكفاءة في العمل / Surveillance de l'état de santé des travailleurs et des apprentis par des examens médicaux périodiques et l'évaluation de l'aptitude au travail</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>طب العمل / Médecine du travail</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، المتمهنون / Salariés, apprentis</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، الوظيفة، تقرير الصحة المهنية / Nom et prénom, date et lieu de naissance, situation familiale, adresse, e-mail, téléphone, fonction, rapport de santé au travail</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>36 شهر (03 سنوات) / 36 mois (3 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>أشغال عمومية / Travaux publics</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>تسيير كاميرات المراقبة / Gestion des caméras de surveillance</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>مراقبة أماكن العمل / Surveillance des lieux de travail</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>تسيير تواجد الكاميرات / Gestion de la présence des caméras</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، الزوار / Salariés, fournisseurs, clients actuels ou potentiels, visiteurs</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>صورة في الفيديو / Image vidéo</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>شهر واحد / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="86" customHeight="1">
+      <c r="A191" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>الاتصالات والمواصلات عبر الأقمار الصناعية / Télécommunications et communications par satellite</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>مراقبة الدخول / Contrôle des accès</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>مراقبة الدخول لضمان سلامة الممتلكات والأشخاص / Contrôle des accès pour assurer la sécurité des biens et des personnes</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، المترشحون، المتمهنون، المتربصون وزوار آخرون / Salariés, fournisseurs, clients actuels ou potentiels, candidats, apprentis, stagiaires et autres visiteurs</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، ترقيم السيارة، نسخة من جواز سفر أجنبي / Nom et prénom, n° CNI/permis de conduire/passeport, immatriculation du véhicule, copie de passeport étranger</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="112" customHeight="1">
+      <c r="A192" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>أشغال الطرق / Travaux routiers</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>السجلات القانونية / Registres légaux</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>تحديث بيانات العمال في السجلات القانونية للمؤسسة / Mise à jour des données des travailleurs dans les registres légaux de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>تسيير السجلات القانونية / Gestion des registres légaux</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان السكن، رقم الضمان الاجتماعي، الوظيفة، الجنس، طبيعة علاقة العمل، مدة العطلة، تاريخ التوظيف، تاريخ انتهاء علاقة العمل، الدخل / Nom et prénom, date et lieu de naissance, adresse, n° sécurité sociale, fonction, sexe, nature de la relation de travail, durée de congé, date de recrutement, date de fin de la relation de travail, revenu</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>أشغال الطرق / Travaux routiers</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>المتابعة التجارية لملفات الزبائن / Suivi commercial des dossiers clients</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، التسمية الاجتماعية، البنك، رقم الحساب البنكي / NIN, nom et prénom, e-mail, téléphone, dénomination sociale, banque, n° compte bancaire</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="47" customHeight="1">
+      <c r="A194" s="4" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>أشغال الطرق / Travaux routiers</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>إدارة الحضور / Gestion de la présence</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>مراقبة ومتابعة الحضور / Contrôle et suivi de la présence</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>تسيير حضور الموظفين / Gestion de la présence des employés</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، المتمهنون/المتربصون / Salariés, apprentis/stagiaires</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، صورة، معطيات بيومترية (الأصبع والوجه)، رقم التسجيل / Nom et prénom, photo, données biométriques (empreinte digitale et visage), matricule</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="73" customHeight="1">
+      <c r="A195" s="4" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>أشغال الطرق / Travaux routiers</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>معالجة النزاعات والاستشارات القانونية / Traitement des litiges et consultations juridiques</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>تسيير قضايا المنازعات والاستشارات القانونية / Gestion des affaires contentieuses et des consultations juridiques</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>تسيير النزاعات والاستشارات القانونية / Gestion des litiges et consultations juridiques</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، ممثلو الشركات المتعاقدة مع المؤسسة / Salariés, représentants des sociétés contractantes avec l'entreprise</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، الجنس، عقد العمل، رقم الحساب البنكي/البريدي / Nom et prénom, date et lieu de naissance, situation familiale, adresse, sexe, contrat de travail, n° compte bancaire/postal</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="86" customHeight="1">
+      <c r="A196" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>أشغال الطرق / Travaux routiers</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>إدارة الموردين ومقدمي الخدمات / Gestion des fournisseurs et prestataires de services</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>إدارة العلاقات مع الموردين ومقدمي الخدمات - الإدارة التجارية وإعداد الفواتير / Gestion des relations avec les fournisseurs et prestataires de services - administration commerciale et facturation</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الموردين، تسيير مقدمي الخدمات / Gestion des fournisseurs, gestion des prestataires de services</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>الموردون، مقدمو الخدمات / Fournisseurs, prestataires de services</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، العنوان، الوظيفة، التسمية الاجتماعية، البنك، رقم الحساب البنكي / NIN, nom et prénom, e-mail, téléphone, adresse, fonction, dénomination sociale, banque, n° compte bancaire</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>أشغال الطرق / Travaux routiers</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>تسيير أوامر بالمهمة / Gestion des ordres de mission</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>تفويض وضمان سلامة التنقل المهني للعمال / Autoriser et assurer la sécurité des déplacements professionnels des travailleurs</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الأوامر بمهمة / Gestion des ordres de mission</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، الوظيفة / Nom et prénom, fonction</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>42 شهر (03 سنوات و06 أشهر) / 42 mois (3 ans et 6 mois)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>أشغال الطرق / Travaux routiers</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>لجنة المشاركة والخدمات الاجتماعية / Comité de participation et des œuvres sociales</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>تحسين الحالة الاجتماعية للعمال وذوي الحقوق / Amélioration de la situation sociale des travailleurs et ayants droit</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الخدمات الاجتماعية / Gestion des œuvres sociales</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، رقم الهاتف / Nom et prénom, date et lieu de naissance, situation familiale, adresse, téléphone</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>42 شهر (03 سنوات و06 أشهر) / 42 mois (3 ans et 6 mois)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="73" customHeight="1">
+      <c r="A199" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>أشغال الطرق / Travaux routiers</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>إدارة المشتريات / Gestion des achats</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>إدارة الطلبات واقتناء المواد الأولية والاستهلاكية والخدمات المختلفة / Gestion des commandes et acquisition des matières premières, consommables et divers services</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>تسيير المشتريات / Gestion des achats</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، العنوان، البنك، رقم الحساب البنكي، رخصة السياقة / NIN, nom et prénom, e-mail, téléphone, adresse, banque, n° compte bancaire, permis de conduire</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>180 شهر (15 سنة) / 180 mois (15 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="138" customHeight="1">
+      <c r="A200" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>أشغال عمومية / Travaux publics</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>إدارة شؤون العمال / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>إدارة العمال / Gestion des travailleurs</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، معطيات بيومترية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، رقم الضمان الاجتماعي، السيرة الذاتية، الراتب، البنك-البريد، رقم الحساب البريدي والبنكي / NIN, nom et prénom, date et lieu de naissance, situation familiale, photo, données biométriques, adresse, e-mail, téléphone, n° CNI/permis de conduire/passeport, n° sécurité sociale, CV, salaire, banque-poste, n° compte postal et bancaire</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="73" customHeight="1">
+      <c r="A201" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>الصناعة الغذائية / Industrie alimentaire</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>التوعية والسلامة الصحية والمهنية لفائدة الموظفين / Sensibilisation et sécurité sanitaire et professionnelle au profit des employés</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>إثراء ثقافة السلامة لدى الموظفين، ضمان حماية الموظفين في مكان العمل / Enrichir la culture de sécurité chez les employés et assurer leur protection sur le lieu de travail</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الصحة والسلامة المهنية والبيئة / Gestion de la santé, de la sécurité au travail et de l'environnement</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>مقدمو الخدمات / Prestataires de services</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، صورة، الوظيفة، الرتبة، رقم التسجيل / Nom et prénom, photo, fonction, grade, matricule</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="112" customHeight="1">
+      <c r="A202" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>الصناعة الغذائية / Industrie alimentaire</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الخدمات الاجتماعية / Gestion des œuvres sociales</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>مساعدة الموظفين وذوي الحقوق على تقليل جزء من نفقاتهم المتعلقة بأمراضهم الخطيرة، تعزيز التزامات الموظفين وتعزيز تماسك الفريق / Aider les employés et ayants droit à réduire une partie de leurs dépenses liées à des maladies graves, renforcer l'engagement des employés et la cohésion d'équipe</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الخدمات الاجتماعية / Gestion des œuvres sociales</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>ذوو حقوق الأجير (الزوج(ة) والأبناء) / Ayants droit du salarié (conjoint et enfants)</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، رقم الهاتف، الوظيفة، الرتبة، رقم التسجيل، الهيكل التنظيمي التابع لها، رأي الطبيب، الدخل، كشف الهوية البنكية / Nom et prénom, date et lieu de naissance, situation familiale, téléphone, fonction, grade, matricule, structure organisationnelle de rattachement, avis du médecin, revenu, relevé d'identité bancaire</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>180 شهر (15 سنة) / 180 mois (15 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="60" customHeight="1">
+      <c r="A203" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>استشارة عروض السوق / Consultation des offres du marché</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>تحليل وتقييم عروض السوق / Analyse et évaluation des offres du marché</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>استشارة السوق / Consultation du marché</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>المتعهدون / Soumissionnaires</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، التوقيع، رقم السجل التجاري / Nom et prénom, e-mail, téléphone, signature, n° registre de commerce</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="99" customHeight="1">
+      <c r="A204" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>إدارة الخبراء والاستشاريين / Gestion des experts et consultants</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>إدارة تدخلات ومهام الخبراء والاستشاريين / Gestion des interventions et missions des experts et consultants</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الخبراء والاستشاريين / Gestion des experts et consultants</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>الاستشاريون، الخبراء / Consultants, experts</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، التوقيع، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، نسخة من بطاقة المقاول الذاتي، السيرة الذاتية، الحساب البنكي / Nom et prénom, adresse, e-mail, téléphone, signature, n° CNI/permis de conduire/passeport, copie de la carte d'auto-entrepreneur, CV, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="60" customHeight="1">
+      <c r="A205" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>حماية الموقع / Protection du site</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>ضمان أمن الموقع وممتلكات الشركة / Assurer la sécurité du site et des biens de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>حماية الموقع / Protection du site</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>الموردون، الزوار، الزبائن الحاليون أو المحتملون / Fournisseurs, visiteurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، نوع المركبة، ترقيم المركبة / Nom et prénom, n° CNI/permis de conduire/passeport, type de véhicule, immatriculation du véhicule</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="60" customHeight="1">
+      <c r="A206" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>إدارة شكاوى العملاء / Gestion des réclamations des clients</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>تسجيل ومعالجة شكاوى العملاء / Enregistrement et traitement des réclamations des clients</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>تسيير شكاوى الزبائن / Gestion des réclamations des clients</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، عنوان السكن، التوقيع، رقم السجل التجاري / Nom et prénom, e-mail, téléphone, adresse, signature, n° registre de commerce</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="60" customHeight="1">
+      <c r="A207" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>إدارة التسويق التشغيلي / Gestion du marketing opérationnel</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>تنفيذ الأنشطة التسويقية الميدانية / Mise en œuvre des activités marketing sur le terrain</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>تسيير التسويق التشغيلي / Gestion du marketing opérationnel</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، التوقيع، صورة / Nom et prénom, e-mail, téléphone, signature, photo</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="138" customHeight="1">
+      <c r="A208" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>توظيف واختيار المرشحين / Recrutement et sélection des candidats</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>استقطاب وتقييم وتوظيف المرشحين / Attirer, évaluer et recruter les candidats</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>تسيير التوظيف / Gestion du recrutement</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>المرشحون / Candidats</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، صحيفة السوابق القضائية، استمارة الوكالة الوطنية للتشغيل، السيرة الذاتية / Nom et prénom, téléphone, e-mail, casier judiciaire, formulaire de l'Agence nationale de l'emploi, CV</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر بالنسبة للاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، استمارة الوكالة الوطنية للتشغيل والسيرة الذاتية؛ 0 شهر بالنسبة لصحيفة السوابق القضائية / 12 mois pour nom et prénom, téléphone, e-mail, formulaire ANEM et CV ; 0 mois pour le casier judiciaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="73" customHeight="1">
+      <c r="A209" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>إدارة الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>إدارة الموردين وضمان جودة التوريدات وتوافقها واستمراريتها / Gestion des fournisseurs et garantie de la qualité, de la conformité et de la continuité des approvisionnements</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، التوقيع، رقم السجل التجاري، الحساب البنكي / Nom et prénom, e-mail, téléphone, n° CNI/permis de conduire/passeport, signature, n° registre de commerce, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="73" customHeight="1">
+      <c r="A210" s="4" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>إدارة الحملات الترويجية وحملات السحب / Gestion des campagnes promotionnelles et des tirages au sort</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>تخطيط وتنظيم وتنسيق الأنشطة التسويقية الهادفة إلى جذب انتباه العملاء / Planification, organisation et coordination des activités marketing visant à attirer l'attention des clients</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الحملات الترويجية وحملات السحب / Gestion des campagnes promotionnelles et des tirages au sort</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، عنوان البريد الإلكتروني / Nom et prénom, adresse, e-mail (liste partiellement visible sur le document)</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
+          <t>غير ظاهرة على الوثيقة / Non visible sur le document</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="99" customHeight="1">
+      <c r="A211" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>تسيير المتمهنين / Gestion des apprentis</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>متابعة وتأطير تكوين المتمهنين / Suivi et encadrement de la formation des apprentis</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>تسيير المتمهنين / Gestion des apprentis</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>المتمهنون / Apprentis</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، صورة، عنوان السكن، رقم الهاتف، التوقيع، نسخة من بطاقة الهوية الوطنية، الحساب البنكي / Nom et prénom, date de naissance, n° CNI/permis de conduire/passeport, photo, adresse, téléphone, signature, copie de la carte d'identité nationale, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>36 شهر (03 سنوات) / 36 mois (3 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="60" customHeight="1">
+      <c r="A212" s="4" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>إعداد التقارير / Élaboration des rapports</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>ضمان إعداد التقارير وتقديمها إلى مجلس الإدارة والمجمع / Assurer l'élaboration des rapports et leur présentation au conseil d'administration et au groupe</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="inlineStr">
+        <is>
+          <t>إعداد وتقديم التقارير / Élaboration et présentation des rapports</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم السجل التجاري، الوظيفة، الدخل / Nom et prénom, n° registre de commerce, fonction, revenu</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="60" customHeight="1">
+      <c r="A213" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>إدارة الفعاليات / Gestion des événements</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>تنظيم وتنسيق الفعاليات الداخلية والخارجية / Organisation et coordination des événements internes et externes</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الفعاليات / Gestion des événements</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، الزبائن الحاليون أو المحتملون / Salariés, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، التوقيع، الوظيفة / Nom et prénom, téléphone, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>03 أشهر / 3 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="73" customHeight="1">
+      <c r="A214" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>الإدارة التجارية / Administration commerciale</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>تطوير وإدارة الأنشطة التجارية / Développement et gestion des activités commerciales</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، التوقيع، رقم السجل التجاري، عنوان البريد الإلكتروني / Nom et prénom, adresse, téléphone, n° CNI/permis de conduire/passeport, signature, n° registre de commerce, e-mail</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="60" customHeight="1">
+      <c r="A215" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>تكييف منصب العمل / Adaptation du poste de travail</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>تكييف المنصب حسب احتياجات الصحة والسلامة / Adaptation du poste selon les besoins de santé et de sécurité</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>تكييف منصب العمل / Adaptation du poste de travail</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، شهادة طبية لتكييف المنصب، الوظيفة / Nom et prénom, certificat médical d'adaptation du poste, fonction</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="60" customHeight="1">
+      <c r="A216" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>المراقبة بالفيديو / Vidéosurveillance</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>ضمان أمن الموقع وممتلكات الشركة / Assurer la sécurité du site et des biens de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>المراقبة عن طريق الفيديو / Surveillance par vidéo</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزوار، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, visiteurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>صور الفيديو / Images vidéo</t>
+        </is>
+      </c>
+      <c r="H216" s="5" t="inlineStr">
+        <is>
+          <t>01 شهر / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="60" customHeight="1">
+      <c r="A217" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>لجنة التأديب / Commission de discipline</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>دراسة ومعاقبة المخالفات التأديبية / Examen et sanction des infractions disciplinaires</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>اللجان التأديبية / Commissions disciplinaires</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، التوقيع، الوظيفة / Nom et prénom, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="60" customHeight="1">
+      <c r="A218" s="4" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>الاستمارة والخدمات الإلكترونية / Formulaires et services électroniques</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>توفير الخدمات والنماذج عبر الإنترنت / Fourniture de services et de formulaires en ligne</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>الاستمارة والخدمات الإلكترونية / Formulaires et services électroniques</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني / Nom et prénom, e-mail</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="60" customHeight="1">
+      <c r="A219" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>إدارة معدات الحماية الفردية / Gestion des équipements de protection individuelle</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>توفير ومراقبة استخدام معدات الحماية الفردية / Fourniture et contrôle de l'utilisation des équipements de protection individuelle</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>تسيير معدات الحماية الفردية / Gestion des équipements de protection individuelle</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، التوقيع، الطول، المقاس / Nom et prénom, signature, taille, mensurations</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>24 شهر (سنتين) / 24 mois (2 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="60" customHeight="1">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>إدارة المخزون / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>مراقبة وتحسين مخزون الشركة / Contrôle et optimisation des stocks de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المخزون / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون / Salariés, fournisseurs</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، التوقيع / Nom et prénom, signature</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="60" customHeight="1">
+      <c r="A221" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>اللجنة المشتركة للصحة والسلامة / Commission paritaire de santé et de sécurité</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>تحسين شروط النظافة والسلامة في العمل / Amélioration des conditions d'hygiène et de sécurité au travail</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>اللجنة المشتركة للصحة والسلامة / Commission paritaire de santé et de sécurité</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، التوقيع، الوظيفة / Nom et prénom, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="60" customHeight="1">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>تحصيل ديون العملاء / Recouvrement des créances clients</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>متابعة واسترجاع الديون من العملاء / Suivi et recouvrement des créances auprès des clients</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>تحصيل ديون الزبائن / Recouvrement des créances des clients</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، التوقيع، رقم السجل التجاري / Nom et prénom, e-mail, téléphone, signature, n° registre de commerce</t>
+        </is>
+      </c>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="60" customHeight="1">
+      <c r="A223" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>إدارة صندوق التحصيل / Gestion de la caisse de recouvrement</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التدفقات المالية للصندوق / Gestion des flux financiers de la caisse</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>تسيير صندوق التحصيل / Gestion de la caisse de recouvrement</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، التوقيع / Nom et prénom, signature</t>
+        </is>
+      </c>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="60" customHeight="1">
+      <c r="A224" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>إدارة التسويق الرقمي / Gestion du marketing digital</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>الترويج للشركة عبر القنوات الرقمية / Promotion de l'entreprise via les canaux numériques</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التسويق الرقمي / Gestion du marketing digital</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>صورة الفيديو، الصوت / Image vidéo, voix</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="60" customHeight="1">
+      <c r="A225" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>خطة الصيانة / Plan de maintenance</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>تخطيط وتنفيذ صيانة المعدات / Planification et exécution de la maintenance des équipements</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>خطة الصيانة / Plan de maintenance</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، الوظيفة / Nom et prénom, téléphone, e-mail, fonction</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="60" customHeight="1">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>أرشيف بيانات العملاء والموردين / Archives des données des clients et fournisseurs</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>حفظ وتأمين أرشيف البيانات / Conservation et sécurisation des archives de données</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>أرشيف بيانات الزبائن والموردين / Archives des données des clients et fournisseurs</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزبائن الحاليون أو المحتملون / Fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، عنوان السكن، رقم السجل التجاري / Nom et prénom, téléphone, e-mail, adresse, n° registre de commerce</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="73" customHeight="1">
+      <c r="A227" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>إدارة خدمة الزبائن / Gestion du service client</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>إدارة تفاعلات المستهلكين لتحسين تجربة العملاء ودعم الأنشطة التسويقية / Gestion des interactions avec les consommateurs pour améliorer l'expérience client et soutenir les activités marketing</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستهلكين / Gestion des consommateurs</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، عنوان السكن / Nom et prénom, téléphone, e-mail, adresse</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="60" customHeight="1">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>دراسة السوق وتطوير المنتجات / Étude de marché et développement des produits</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>تحليل السوق ومدى رضا الزبائن عن المنتجات / Analyse du marché et de la satisfaction des clients à l'égard des produits</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الاستطلاعات ودراسة السوق / Gestion des sondages et des études de marché</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، عنوان السكن، الجنس / Nom et prénom, téléphone, e-mail, adresse, sexe</t>
+        </is>
+      </c>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="99" customHeight="1">
+      <c r="A229" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>التمثيلية القانونية / Représentation juridique</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الإجراءات القانونية والتمثيل القانوني للمؤسسة أمام الهيئات المختصة / Gestion des procédures juridiques et représentation légale de l'entreprise devant les instances compétentes</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>التمثيلية القانونية / Représentation juridique</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، عنوان البريد الإلكتروني، عنوان السكن، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، التوقيع، اسم ولقب الأب، اسم ولقب الأم، رقم السجل التجاري / Nom et prénom, date de naissance, e-mail, adresse, téléphone, n° CNI/permis de conduire/passeport, signature, nom et prénom du père, nom et prénom de la mère, n° registre de commerce</t>
+        </is>
+      </c>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="60" customHeight="1">
+      <c r="A230" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>تسيير تطوير الكفاءات / Gestion du développement des compétences</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>تطوير الكفاءات للعمال عن طريق التكوين / Développement des compétences des travailleurs par la formation</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>تسيير تطوير الكفاءات / Gestion du développement des compétences</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، التوقيع، الوظيفة / Nom et prénom, e-mail, téléphone, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H230" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="125" customHeight="1">
+      <c r="A231" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>البريد السريع / Courrier express</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>تتبع المركبات المهنية للشركة عبر نظام تحديد الموقع الجغرافي / Suivi des véhicules professionnels de l'entreprise via un système de géolocalisation</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>متابعة المركبات المهنية في الوقت الفعلي لتأمين السائقين والممتلكات، تحسين التنقلات وضمان إمكانية التتبع في حال وقوع أي حادث، وفقًا للقانون / Suivi en temps réel des véhicules professionnels afin de sécuriser les conducteurs et les biens, d'optimiser les déplacements et de garantir la traçabilité en cas d'accident, conformément à la loi</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموارد المهنية (أسطول المركبات) / Gestion des ressources professionnelles (flotte de véhicules)</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، عمال التوصيل المستقلون الذين يستخدمون مركبات الشركة / Salariés, livreurs indépendants utilisant les véhicules de l'entreprise</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، الإحداثيات الجغرافية، رقم التسجيل، ساعات السياقة وفترات الراحة، الرحلات المنجزة، الوضعية المهنية (موظف/عامل توصيل مستقل)، علامة المركبة / Nom et prénom, téléphone, coordonnées géographiques, matricule, heures de conduite et périodes de repos, trajets effectués, statut professionnel (employé/livreur indépendant), marque du véhicule</t>
+        </is>
+      </c>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>24 شهر (سنتين) / 24 mois (2 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="190" customHeight="1">
+      <c r="A232" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>البريد السريع / Courrier express</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الإجراءات التأديبية والنزاعات الخاصة بالموظفين / Gestion des procédures disciplinaires et des litiges relatifs aux employés</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>ضمان متابعة وإدارة وتتبع الإجراءات التأديبية والنزاعات المتعلقة بالموظفين وفقًا لتشريع العمل والتنظيم الداخلي / Assurer le suivi, la gestion et la traçabilité des procédures disciplinaires et des litiges relatifs aux employés conformément à la législation du travail et au règlement intérieur</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، معطيات بيومترية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، تسجيلات الفيديوهات، التوقيعات، الوثائق التبريرية والأدلة، الوظيفة، مقر التعيين، استمارة تقييم، السوابق التأديبية، الشهادات، تاريخ التوظيف، بطاقة الوصف الوظيفي / Nom et prénom, date et lieu de naissance, situation familiale, photo, données biométriques, adresse, e-mail, téléphone, n° CNI/permis de conduire/passeport, enregistrements vidéo, signatures, pièces justificatives et preuves, fonction, lieu d'affectation, formulaire d'évaluation, antécédents disciplinaires, diplômes, date de recrutement, fiche de poste</t>
+        </is>
+      </c>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) لمعظم المعطيات؛ 12 شهر بالنسبة لتسجيلات الفيديوهات والوثائق التبريرية والأدلة / 120 mois (10 ans) pour la plupart des données ; 12 mois pour les enregistrements vidéo, les pièces justificatives et les preuves</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="86" customHeight="1">
+      <c r="A233" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج / Production</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>المعلومات الشخصية للعمال / Informations personnelles des travailleurs</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين والأجور / Gestion du personnel et des salaires</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، صورة، عنوان السكن، الحالة العائلية، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الوظيفة، السيرة الذاتية، الحساب البنكي / Nom et prénom, date de naissance, photo, adresse, situation familiale, n° CNI/permis de conduire/passeport, fonction, CV, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>504 شهر (42 سنة) / 504 mois (42 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="125" customHeight="1">
+      <c r="A234" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>صناعة المنتجات الإلكترونية / Fabrication de produits électroniques</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>إدارة نظام الجودة، النظافة، السلامة والبيئة / Gestion du système qualité, hygiène, sécurité et environnement</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>إدارة نظام جودة، نظافة، سلامة وبيئة وفقًا للمعايير الدولية والتشريعات المعمول بها / Gestion d'un système qualité, hygiène, sécurité et environnement conformément aux normes internationales et aux législations en vigueur</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>مراقبة نظام إدارة الجودة، النظافة، السلامة والبيئة وفقًا للمعايير الدولية والتشريعات المعمول بها / Contrôle du système de management qualité, hygiène, sécurité et environnement conformément aux normes internationales et aux législations en vigueur</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، تاريخ ومكان الازدياد، الوظيفة / Nom et prénom, e-mail, date et lieu de naissance, fonction</t>
+        </is>
+      </c>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="99" customHeight="1">
+      <c r="A235" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>صناعة المنتجات الإلكترونية / Fabrication de produits électroniques</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>إدارة نظام المراقبة بالفيديو / Gestion du système de vidéosurveillance</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن الأفراد والممتلكات في مقرات الشركة / Assurer la sécurité des personnes et des biens dans les locaux de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، الزوار، وكل شخص آخر يدخل إلى مقرات الشركة / Salariés, fournisseurs, clients actuels ou potentiels, visiteurs et toute autre personne accédant aux locaux de l'entreprise</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>صورة، رقم لوحة تسجيل المركبة / Image, numéro d'immatriculation du véhicule</t>
+        </is>
+      </c>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>شهر واحد / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="125" customHeight="1">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>صناعة المنتجات الإلكترونية / Fabrication de produits électroniques</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>استقطاب الموظفين / Recrutement du personnel</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>القيام بعملية استقطاب المرشحين لشغل الوظائف الشاغرة، مع ضمان مواءمة مؤهلاتهم وخبراتهم مع متطلبات المناصب المتاحة / Mener le processus de recrutement des candidats pour pourvoir les postes vacants, en veillant à l'adéquation de leurs qualifications et de leur expérience avec les exigences des postes disponibles</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>إدارة عمليات التوظيف / Gestion des opérations de recrutement</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>المترشحون / Candidats</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، رقم الهاتف، شهادات الجامعة وشهادات التكوين / Nom et prénom, date et lieu de naissance, situation familiale, photo, adresse, téléphone, diplômes universitaires et attestations de formation</t>
+        </is>
+      </c>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="112" customHeight="1">
+      <c r="A237" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>صناعة الأدوية / Industrie pharmaceutique</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة وإدارة الخزينة / Comptabilité et gestion de la trésorerie</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المحاسبة والخزينة الخاصة بالمؤسسة / Gestion de la comptabilité et de la trésorerie de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة وتسيير الخزينة / Comptabilité et gestion de la trésorerie</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، نسخة من وثيقة الهوية الوطنية، التوقيع، رقم السجل التجاري، الحساب البنكي، رقم التعريف الجبائي / Nom et prénom, adresse, e-mail, téléphone, n° CNI/permis de conduire/passeport, copie de la pièce d'identité nationale, signature, n° registre de commerce, compte bancaire, NIF</t>
+        </is>
+      </c>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="125" customHeight="1">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>صناعة الأدوية / Industrie pharmaceutique</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>إستضافة ومشاركة وحفظ البيانات / Hébergement, partage et conservation des données</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>إستضافة، مشاركة وحفظ البيانات / Hébergement, partage et conservation des données</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>تسيير إستضافة المعطيات ومشاركتها وحفظها / Gestion de l'hébergement, du partage et de la conservation des données</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، معطيات الموارد البشرية (ملفات الأجراء، التقييمات، العطل، الوثائق الإدارية)، المعطيات التقنية (سجلات النظام، معرفات المستخدمين، عناوين بروتوكول الأنترنت الداخلية)، الوظيفة / Nom et prénom, adresse, e-mail, téléphone, données RH (dossiers des salariés, évaluations, congés, documents administratifs), données techniques (journaux système, identifiants utilisateurs, adresses IP internes), fonction</t>
+        </is>
+      </c>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="47" customHeight="1">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>صناعة الأدوية / Industrie pharmaceutique</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>الاتصال / Communication</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>تسهيل وتنظيم الاتصال الداخلي والخارجي / Faciliter et organiser la communication interne et externe</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>الاتصال / Communication</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الزبائن الحاليون أو المحتملون / Salariés, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، عنوان السكن / Nom et prénom, e-mail, téléphone, adresse</t>
+        </is>
+      </c>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="47" customHeight="1">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>صناعة الأدوية / Industrie pharmaceutique</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>اللجنة المشتركة للصحة والسلامة / Commission paritaire de santé et de sécurité</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>متابعة أعمال اللجنة المشتركة للصحة والسلامة / Suivi des travaux de la commission paritaire de santé et de sécurité</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>اللجنة المشتركة للصحة والسلامة / Commission paritaire de santé et de sécurité</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، التوقيع، الوظيفة / Nom et prénom, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="86" customHeight="1">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>صناعة الأدوية / Industrie pharmaceutique</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>حماية الموقع / Protection du site</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن وحماية الموقع / Assurer la sûreté et la protection du site</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>أمن الموقع / Sécurité du site</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزبائن الحاليون أو المحتملون، الزوار / Fournisseurs, clients actuels ou potentiels, visiteurs</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، نوع المركبة، رقم تسجيل المركبة، نسخة من بطاقة الإقامة للأجانب، نسخة من جواز السفر / Nom et prénom, n° CNI/permis de conduire/passeport, type de véhicule, immatriculation du véhicule, copie de la carte de résidence pour les étrangers, copie du passeport</t>
+        </is>
+      </c>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="99" customHeight="1">
+      <c r="A242" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>صناعة المنتجات الصيدلانية / Fabrication de produits pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>تسيير لجنة المشاركة / Gestion du comité de participation</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الخدمات الاجتماعية لفائدة الموظفين من أجل تحسين رفاهيتهم وتعزيز التماسك الاجتماعي داخل المؤسسة / Gestion des œuvres sociales au profit des employés afin d'améliorer leur bien-être et de renforcer la cohésion sociale au sein de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>تسيير لجنة المشاركة / Gestion du comité de participation</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، شهادة وفاة، جواز السفر، رقم التعريف الوطني، عنوان البريد الإلكتروني، الحساب البنكي، المبلغ / Nom et prénom, date et lieu de naissance, acte de décès, passeport, NIN, e-mail, compte bancaire, montant</t>
+        </is>
+      </c>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="99" customHeight="1">
+      <c r="A243" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المياه المعدنية ومياه الينابيع / Production d'eaux minérales et d'eaux de source</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة وإدارة الخزينة / Comptabilité et gestion de la trésorerie</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>ضمان إدارة مالية فعالة من خلال مراقبة تدفقات الأموال / Assurer une gestion financière efficace par le contrôle des flux de fonds</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة وتسيير الخزينة / Comptabilité et gestion de la trésorerie</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، أعضاء مجلس الإدارة، المساهمون / Fournisseurs, membres du conseil d'administration, actionnaires</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، التوقيع، نسخة من بطاقة الهوية الوطنية، رقم السجل التجاري، الحساب البنكي / Nom et prénom, adresse, e-mail, téléphone, n° CNI/permis de conduire/passeport, signature, copie de la carte d'identité nationale, n° registre de commerce, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H243" s="3" t="inlineStr">
         <is>
           <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
         </is>

--- a/backend/processing/fixtures/processing_templates.xlsx
+++ b/backend/processing/fixtures/processing_templates.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende - دليل" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BDD Traitements'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BDD Traitements'!$A$1:$H$363</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10254,8 +10254,4808 @@
         </is>
       </c>
     </row>
+    <row r="244" ht="60" customHeight="1">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>التجارة الإلكترونية / Commerce électronique</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>معالجة الفواتير / Traitement des factures</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>متابعة الدفعات والمعاملات المالية / Suivi des paiements et des transactions financières</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة، تسيير الموردين، تسيير الزبائن / Comptabilité, gestion des fournisseurs, gestion des clients</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزبائن الحاليون أو المحتملون / Fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>السجل التجاري، شهادة الوجود، رقم التعريف الضريبي، رقم التعريف الإحصائي / Registre de commerce, attestation d'existence, NIF, NIS</t>
+        </is>
+      </c>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="125" customHeight="1">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>البريد السريع / Courrier express</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>إدارة التوظيف عبر الوكالة الوطنية للتشغيل والطلبات المباشرة / Gestion du recrutement via l'Agence nationale de l'emploi et les candidatures spontanées</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>تنظيم وإدارة عملية التوظيف من استقبال الطلبات إلى التعيين / Organisation et gestion du processus de recrutement, de la réception des candidatures à la nomination</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التوظيف / Gestion du recrutement</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>المترشحون / Candidats</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الشهادات، السيرة الذاتية، الخبرة المهنية، التكوين، استمارة التسجيل ANEM / Nom et prénom, date et lieu de naissance, situation familiale, photo, adresse, e-mail, téléphone, n° CNI/permis de conduire/passeport, diplômes, CV, expérience professionnelle, formation, formulaire d'inscription ANEM</t>
+        </is>
+      </c>
+      <c r="H245" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="60" customHeight="1">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>البريد السريع / Courrier express</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>المراقبة بالفيديو / Vidéosurveillance</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن الأشخاص والممتلكات والمباني / Assurer la sécurité des personnes, des biens et des bâtiments</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، الزوار / Salariés, fournisseurs, clients actuels ou potentiels, visiteurs</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>فيديو / Vidéo</t>
+        </is>
+      </c>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>03 أشهر / 3 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="99" customHeight="1">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>البريد السريع / Courrier express</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الأجور والرواتب / Gestion des salaires et de la paie</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>ضمان التسيير الإداري والمالي لأجور الموظفين مع احترام الإلتزامات القانونية والجبائية والاجتماعية / Assurer la gestion administrative et financière des salaires des employés dans le respect des obligations légales, fiscales et sociales</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، رقم الضمان الاجتماعي، الوظيفة، رقم التسجيل الداخلي (رقم الموظف)، الدخل، الحساب البنكي / Nom et prénom, date et lieu de naissance, situation familiale, adresse, n° sécurité sociale, fonction, matricule interne (n° employé), revenu, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="73" customHeight="1">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>البريد السريع / Courrier express</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزوار / Gestion des visiteurs</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن المقرات والأشخاص / Assurer la sécurité des locaux et des personnes</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزبائن الحاليون أو المحتملون، الزوار الخارجيون / Fournisseurs, clients actuels ou potentiels, visiteurs externes</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، تاريخ الزيارة، وقت الدخول والخروج، توقيع الزوار / Nom et prénom, n° CNI/permis de conduire/passeport, date de la visite, heures d'entrée et de sortie, signature des visiteurs</t>
+        </is>
+      </c>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>03 أشهر / 3 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="294" customHeight="1">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>خدمات / Services</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموارد البشرية / Gestion des ressources humaines</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>تحديد هوية الموظفين، إدارة وصولهم، وتبسيط الاتصالات الداخلية، وإدارة الموارد البشرية من الرواتب إلى الوظائف، بما في ذلك الالتزامات الاجتماعية والإدارية / Identification des employés, gestion de leurs accès, simplification des communications internes et gestion des ressources humaines, de la paie aux fonctions, y compris les obligations sociales et administratives</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، معطيات بيومترية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الاتصال في حالة الطوارئ (اسم ولقب الأشخاص ذوي الحقوق: الوالدين، الأبناء، الأزواج/الزوجات، أو أشخاص آخرين متكفل بهم)، رقم الضمان الاجتماعي، رقم التعريف الوطني، الجنسية، شهادة إقامة، مستخرج عقد الميلاد، الوظيفة، رقم تسجيل (رمز الموظف، الزبون، المورد)، شهادة، استمارة التسجيل في الوكالة الوطنية للتشغيل، التكوين، الأجر، الهيئة، المؤسسة، الأقدمية، كشف الهوية البنكية، كشف الهوية البريدية، رقم الحساب المصرفي الدولي، رقم الحساب / Nom et prénom, date et lieu de naissance, situation familiale, photo, données biométriques, adresse, e-mail, téléphone, n° CNI/permis de conduire/passeport, contact d'urgence (nom et prénom des ayants droit : parents, enfants, conjoints ou autres personnes à charge), n° sécurité sociale, NIN, nationalité, certificat de résidence, extrait d'acte de naissance, fonction, matricule (code employé, client, fournisseur), diplôme, formulaire d'inscription ANEM, formation, salaire, organisme, entreprise, ancienneté, RIB, RIP, IBAN, n° de compte</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="112" customHeight="1">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>صناعة اللافتات الاشهارية / Fabrication d'enseignes publicitaires</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>المراقبة بالفيديو / Vidéosurveillance</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن الأشخاص، الممتلكات، المباني، والوقاية من أعمال التخريب أو السرقة أو الإتلاف، والتحكم في الدخول إلى الفضاءات المهنية / Assurer la sécurité des personnes, des biens et des bâtiments, prévenir les actes de vandalisme, de vol ou de dégradation et contrôler l'accès aux espaces professionnels</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، الأشخاص الأجانب / Salariés, fournisseurs, clients actuels ou potentiels, personnes étrangères</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>صورة / Image</t>
+        </is>
+      </c>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>شهر واحد / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="112" customHeight="1">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>صناعة اللافتات الاشهارية / Fabrication d'enseignes publicitaires</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>ضمان التسيير الإداري، المحاسبي، والتعاقدي للعلاقات مع الموردين / Assurer la gestion administrative, comptable et contractuelle des relations avec les fournisseurs</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، الوظيفة، المستخدم، الحساب البنكي / Nom et prénom, fonction, employeur, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) بالنسبة للاسم واللقب، الوظيفة والمستخدم؛ 120 شهر (10 سنوات) بالنسبة للحساب البنكي / 60 mois (5 ans) pour nom et prénom, fonction et employeur ; 120 mois (10 ans) pour le compte bancaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="203" customHeight="1">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>صناعة اللافتات الاشهارية / Fabrication d'enseignes publicitaires</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الموظفين والأجور / Gestion du personnel et des salaires</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>ضمان إدارة شؤون الموظفين والأجور / Assurer la gestion du personnel et des salaires</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، الحالة العائلية، عنوان السكن، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، السيرة الذاتية، رقم التعريف الوطني، شهادات العمل، الشهادات / Nom et prénom, date de naissance, situation familiale, adresse, n° CNI/permis de conduire/passeport, CV, NIN, certificats de travail, diplômes</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>03 أشهر بالنسبة للاسم واللقب، تاريخ الازدياد، الحالة العائلية، عنوان السكن ورقم وثيقة الهوية/رخصة السياقة/جواز السفر؛ شهرين بالنسبة للسيرة الذاتية؛ 01 شهر بالنسبة لرقم التعريف الوطني، شهادات العمل والشهادات / 3 mois pour nom et prénom, date de naissance, situation familiale, adresse et n° CNI/permis/passeport ; 2 mois pour le CV ; 1 mois pour le NIN, les certificats de travail et les diplômes</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="99" customHeight="1">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>صناعة اللافتات الاشهارية / Fabrication d'enseignes publicitaires</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التسويق / Gestion du marketing</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>تسيير النشاط التجاري للمؤسسة، بما في ذلك متابعة المبيعات، العروض، الطلبيات، التسليم، الفوترة والدفع / Gestion de l'activité commerciale de l'entreprise, y compris le suivi des ventes, des offres, des commandes, de la livraison, de la facturation et du paiement</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، الوظيفة، المستخدم، الحساب البنكي / Nom et prénom, e-mail, téléphone, fonction, employeur, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="138" customHeight="1">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>الصناعة / Industrie</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الموظفين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>ميكنة وتنظيم وإدارة الأنشطة المرتبطة بالتسيير الإداري للموظفين مع ضمان الالتزام بالقوانين واللوائح الداخلية / Automatisation, organisation et gestion des activités liées à la gestion administrative des employés, en garantissant le respect des lois et du règlement intérieur</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، صورة، الحالة العائلية، عنوان السكن، عنوان البريد الإلكتروني، معطيات بيو مترية، الاسم واللقب (الزوج(ة)/الأبناء)، تاريخ الميلاد (الزوج(ة)/الأبناء)، رقم التسجيل، السيرة الذاتية، الوظيفة، المستخدم، الدخل، الحساب البنكي / NIN, nom et prénom, date et lieu de naissance, photo, situation familiale, adresse, e-mail, données biométriques, nom et prénom (conjoint/enfants), date de naissance (conjoint/enfants), matricule, CV, fonction, employeur, revenu, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="138" customHeight="1">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>تقديم الخدمات في مختلف المجالات / Prestation de services dans divers domaines</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموارد البشرية / Gestion des ressources humaines</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>توفير الإدارة الشاملة لشؤون الموظفين بدءًا من التعيين وحتى إنهاء الخدمة، مع ضمان الالتزام وتقديم الدعم الأمثل / Assurer la gestion globale des affaires du personnel, du recrutement jusqu'à la fin de service, en garantissant la conformité et un accompagnement optimal</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين، المحاسبة / Gestion du personnel, comptabilité</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان السكن، معطيات بيومترية، صورة، الحالة العائلية، تاريخ ومكان الازدياد، معلومات عن الزوج(ة) والأبناء، عنوان البريد الإلكتروني، الوظيفة، المستخدم، السيرة الذاتية، الشهادة، الدخل، رقم البطاقة البنكية، كشف الهوية البنكية / Nom et prénom, téléphone, adresse, données biométriques, photo, situation familiale, date et lieu de naissance, informations sur le conjoint et les enfants, e-mail, fonction, employeur, CV, diplôme, revenu, n° de carte bancaire, RIB</t>
+        </is>
+      </c>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
+          <t>600 شهر (50 سنة) / 600 mois (50 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="60" customHeight="1">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>تقديم الخدمات في مختلف المجالات / Prestation de services dans divers domaines</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>الاستكشاف التجاري / Prospection commerciale</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>اكتساب عملاء جدد، وتحديد فرص سوقية جديدة / Acquisition de nouveaux clients et identification de nouvelles opportunités de marché</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الاستكشاف التجاري / Gestion de la prospection commerciale</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، الوظيفة / Nom et prénom, téléphone, e-mail, fonction</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="86" customHeight="1">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>التجارة الإلكترونية / Commerce électronique</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>الجزمة الجبائية وتصريح G50 / Liasse fiscale et déclaration G50</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>إعداد الجزمة الجبائية وتصريح G50 / Établissement de la liasse fiscale et de la déclaration G50</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة، الجزمة الجبائية وتصريح G50 / Comptabilité, liasse fiscale et déclaration G50</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، مقدمو الخدمات / Fournisseurs, prestataires de services</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، رقم الاعتماد، رقم التعريف الجبائي، رقم المادة الخاضعة للضريبة، المبلغ السنوي للخدمة، مبلغ الضريبة على القيمة المضافة / Nom et prénom, adresse, n° d'agrément, NIF, n° d'article imposable, montant annuel de la prestation, montant de la TVA</t>
+        </is>
+      </c>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="47" customHeight="1">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>التجارة الإلكترونية / Commerce électronique</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>محضر تنصيب لجنة المشاركة / Procès-verbal d'installation du comité de participation</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>تنصيب وتعيين مندوبي العمال / Installation et désignation des délégués du personnel</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>تسيير لجنة المشاركة / Gestion du comité de participation</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب / Nom et prénom</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>36 شهر (03 سنوات) / 36 mois (3 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="73" customHeight="1">
+      <c r="A259" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>التجارة الإلكترونية / Commerce électronique</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الدفاتر القانونية والتنظيمية / Gestion des registres légaux et réglementaires</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>ضمان امتثال الشركة للالتزامات القانونية والتنظيمية / Assurer la conformité de l'entreprise aux obligations légales et réglementaires</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الدفاتر القانونية والتنظيمية / Gestion des registres légaux et réglementaires</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، رقم الضمان الاجتماعي، تاريخ الدخول والخروج، سبب الخروج، الوظيفة، الدخل / Nom et prénom, date de naissance, n° sécurité sociale, dates d'entrée et de sortie, motif de sortie, fonction, revenu</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="47" customHeight="1">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>التجارة الإلكترونية / Commerce électronique</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>المخصصات القانونية للجنة المشاركة / Dotations légales du comité de participation</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الخدمات الاجتماعية / Gestion des œuvres sociales</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>تسيير لجنة المشاركة / Gestion du comité de participation</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، كشف الهوية البنكية / Nom et prénom, adresse, relevé d'identité bancaire</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>شهر واحد / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="138" customHeight="1">
+      <c r="A261" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>صيانة صناعية / Maintenance industrielle</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>تسيير مستخدمي المنصة / Gestion des utilisateurs de la plateforme</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>ربط الباحثين عن العمل بالشركات / Mise en relation des demandeurs d'emploi avec les entreprises</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion des utilisateurs</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>المستخدمون / Utilisateurs</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، أصناف رخصة السياقة، ملكية مركبة، الوضعية تجاه الخدمة الوطنية، رقم التعريف الوطني، السيرة الذاتية، الوظيفة، المنصب المراد شغله، قابلية التنقل، التوفر / Nom et prénom, e-mail, téléphone, date et lieu de naissance, situation familiale, photo, adresse, catégories du permis de conduire, possession d'un véhicule, situation vis-à-vis du service national, NIN, CV, fonction, poste recherché, mobilité, disponibilité</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="112" customHeight="1">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المنتجات الغذائية / Production de produits alimentaires</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>إدارة العمليات البنكية / Gestion des opérations bancaires</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>ضمان إدارة الحسابات البنكية وتنفيذ العمليات المالية ومتابعة العلاقات مع البنوك والامتثال للالتزامات القانونية والمحاسبية / Assurer la gestion des comptes bancaires, l'exécution des opérations financières, le suivi des relations avec les banques et la conformité aux obligations légales et comptables</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة / Comptabilité</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، المسيرون/الممثلون القانونيون للمؤسسة / Salariés, fournisseurs, clients actuels ou potentiels, dirigeants/représentants légaux de l'entreprise</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، عنوان السكن، تاريخ ومكان الازدياد، كشف الهوية البريدية، الوظيفة، الدخل، الحساب البنكي / Nom et prénom, adresse, date et lieu de naissance, relevé d'identité postale, fonction, revenu, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="86" customHeight="1">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>مكتب استشارة في الموارد البشرية / Cabinet de conseil en ressources humaines</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الخبراء والمستشارين الزبائن / Gestion des experts et consultants clients</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>تنظيم وتتبع وتسيير إداري، تعاقدي ومالي للخبراء والمستشارين المتعاملين مع الهيئة / Organisation, suivi et gestion administrative, contractuelle et financière des experts et consultants collaborant avec l'organisme</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الخبراء والاستشاريين / Gestion des experts et consultants</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>الخبراء، الاستشاريون / Experts, consultants</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>تاريخ ومكان الازدياد، صورة، عنوان البريد الإلكتروني، رقم الهاتف، الاسم واللقب، نسخة من بطاقة المقاول الذاتي، السيرة الذاتية، الوظيفة، الحساب البنكي / Date et lieu de naissance, photo, e-mail, téléphone, nom et prénom, copie de la carte d'auto-entrepreneur, CV, fonction, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="112" customHeight="1">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>مكتب استشارة في الموارد البشرية / Cabinet de conseil en ressources humaines</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>إدارة التسويق الرقمي / Gestion du marketing digital</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>ضمان تسيير ومتابعة حملات التسويق الرقمي، تحليل الأداء، تسيير المشتركين/العملاء، وتحسين الاتصال التجاري / Assurer la gestion et le suivi des campagnes de marketing digital, l'analyse des performances, la gestion des abonnés/clients et l'amélioration de la communication commerciale</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التسويق الرقمي / Gestion du marketing digital</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>عنوان البريد الإلكتروني، رقم الهاتف / E-mail, téléphone</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="99" customHeight="1">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>مكتب استشارة في الموارد البشرية / Cabinet de conseil en ressources humaines</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>معطيات العمال / Données des travailleurs</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>تسيير إداري واجتماعي للعمال / Gestion administrative et sociale des travailleurs</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين، الصحة والسلامة في العمل / Gestion du personnel, santé et sécurité au travail</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، معطيات بيومترية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، السيرة الذاتية، الحساب البنكي / NIN, nom et prénom, date et lieu de naissance, situation familiale, photo, données biométriques, adresse, e-mail, téléphone, CV, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="99" customHeight="1">
+      <c r="A266" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>مكتب استشارة في الموارد البشرية / Cabinet de conseil en ressources humaines</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>إدارة ومتابعة العلاقة مع الزبائن (الفوترة، متابعة الطلبيات، خدمات ما بعد البيع، التواصل التجاري والمحافظة على الزبائن) / Gestion et suivi de la relation client (facturation, suivi des commandes, service après-vente, communication commerciale et fidélisation)</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، رقم السجل التجاري / Nom et prénom, e-mail, téléphone, n° registre de commerce</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="86" customHeight="1">
+      <c r="A267" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>مكتب استشارة في الموارد البشرية / Cabinet de conseil en ressources humaines</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>التوظيف واختيار المترشحين / Recrutement et sélection des candidats</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>تحديد، تقييم، واختيار المترشحين الذين يستجيبون لاحتياجات المؤسسة من حيث الكفاءات / Identifier, évaluer et sélectionner les candidats répondant aux besoins de l'entreprise en matière de compétences</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التوظيف / Gestion du recrutement</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>المترشحون / Candidats</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، السيرة الذاتية / Nom et prénom, e-mail, téléphone, CV</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="60" customHeight="1">
+      <c r="A268" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>سياحة / Tourisme</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الأنظمة المعلوماتية / Gestion des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>ضمان تشغيل وأمن وفعالية الأنظمة المعلوماتية / Assurer le fonctionnement, la sécurité et l'efficacité des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الأنظمة المعلوماتية / Gestion des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني المهني / Nom et prénom, adresse e-mail professionnelle</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="73" customHeight="1">
+      <c r="A269" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>تصنيع وتسويق الكابلات الهاتفية والألياف البصرية / Fabrication et commercialisation de câbles téléphoniques et de fibres optiques</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>إدارة تكوينات الموظفين / Gestion des formations des employés</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>تخطيط وتنظيم ومتابعة أنشطة التدريب الداخلي والخارجي / Planification, organisation et suivi des activités de formation interne et externe</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>تسيير تكوينات المستخدمين / Gestion des formations du personnel</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، تاريخ الازدياد، عنوان البريد الإلكتروني، التوقيع، الوظيفة / Nom et prénom, date de naissance, e-mail, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="138" customHeight="1">
+      <c r="A270" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>تصنيع وتسويق الكابلات الهاتفية والألياف البصرية / Fabrication et commercialisation de câbles téléphoniques et de fibres optiques</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>إدارة التأمين التكميلي للصحة / Gestion de l'assurance santé complémentaire</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الانخراط والمتابعة وتقديم خدمات التأمين التكميلي لشركة طالا للتأمين، وذلك لضمان توفير تغطية إضافية للموظفين إلى جانب أنظمة الضمان الاجتماعي / Gestion de l'adhésion, du suivi et de la fourniture des prestations d'assurance complémentaire auprès de la société Taala Assurances, afin d'assurer aux employés une couverture supplémentaire aux régimes de sécurité sociale</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التأمين التكميلي للصحة / Gestion de l'assurance santé complémentaire</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، تاريخ الازدياد، الحالة العائلية، عنوان السكن، لقب الزوج(ة)، تاريخ ميلاد الزوج(ة)، لقب الأبناء، تاريخ ميلاد الأبناء، التوقيع، الوظيفة / Nom et prénom, date de naissance, situation familiale, adresse, nom du conjoint, date de naissance du conjoint, nom des enfants, date de naissance des enfants, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="73" customHeight="1">
+      <c r="A271" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>تصنيع وتسويق الكابلات الهاتفية والألياف البصرية / Fabrication et commercialisation de câbles téléphoniques et de fibres optiques</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>الشريك الاجتماعي النقابي / Partenaire social syndical</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>ضمان إدارة العلاقات الاجتماعية والحوار بين المؤسسة وممثلي النقابات / Assurer la gestion des relations sociales et du dialogue entre l'entreprise et les représentants syndicaux</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>الشريك الاجتماعي النقابي / Partenaire social syndical</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>الإسم واللقب، رقم الهاتف، التوقيع، الوظيفة / Nom et prénom, téléphone, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="112" customHeight="1">
+      <c r="A272" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>حقن ونفخ البلاستيك والأدوات المدرسية / Injection et soufflage de plastique et fournitures scolaires</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>المعلومات الشخصية للعمال / Informations personnelles des travailleurs</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>تسيير شؤون المستخدمين والأجور / Gestion du personnel et des salaires</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، رقم التعريف الوطني، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الشهادة أو المستوى الدراسي، شهادة الأهلية للعمل، السيرة الذاتية، الحساب البنكي / Nom et prénom, date et lieu de naissance, situation familiale, photo, adresse, NIN, n° CNI/permis de conduire/passeport, diplôme ou niveau scolaire, certificat d'aptitude au travail, CV, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>504 أشهر (42 سنة) / 504 mois (42 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="73" customHeight="1">
+      <c r="A273" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>الصناعة الغذائية / Industrie agroalimentaire</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>الأحداث التسويقية والعروض الترويجية / Événements marketing et offres promotionnelles</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>جمع ومعالجة المعطيات في سياق المسابقات أو العروض الترويجية أو المبادرات / Collecte et traitement des données dans le cadre de concours, d'offres promotionnelles ou d'initiatives</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الفعاليات والعروض الترويجية / Gestion des événements et des offres promotionnelles</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، المتابعون على مواقع التواصل الاجتماعي / Salariés, abonnés sur les réseaux sociaux</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، عنوان السكن / Nom et prénom, e-mail, téléphone, adresse</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="60" customHeight="1">
+      <c r="A274" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>الصناعة الغذائية / Industrie agroalimentaire</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>قياس رضا الزبائن / Mesure de la satisfaction des clients</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>قياس رضا الزبائن والحصول على مدى وفائهم / Mesurer la satisfaction des clients et évaluer leur fidélité</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستهلكين / Gestion des consommateurs</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون، المتابعة على وسائل التواصل الاجتماعي / Clients actuels ou potentiels, abonnés sur les réseaux sociaux</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، الولاية، الجنس، الفئة العمرية / Nom et prénom, téléphone, wilaya, sexe, tranche d'âge</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="125" customHeight="1">
+      <c r="A275" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>الصناعة الغذائية / Industrie agroalimentaire</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>معالجة البريد الإداري / Traitement du courrier administratif</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>معالجة المراسلات الواردة من المصالح الجبائية والهيئات الاجتماعية، إعداد وتقديم التصريحات الجبائية / Traitement des correspondances émanant des services fiscaux et des organismes sociaux, préparation et dépôt des déclarations fiscales</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>معالجة البريد الإداري / Traitement du courrier administratif</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، صورة، البطاقة الجبائية، رقم التعريف الجبائي، رقم السجل التجاري، رقم التعريف الإحصائي، شهادة الخضوع الضريبي، القوانين الأساسية، كشف الهوية البنكية/كشف الهوية البريدية الميزانية، مستخرج من الجدول الضريبي / Nom et prénom, date et lieu de naissance, photo, carte fiscale, NIF, n° registre de commerce, NIS, attestation d'assujettissement à l'impôt, statuts, RIB/RIP, bilan, extrait de rôle fiscal</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>180 شهر (15 سنة) / 180 mois (15 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="86" customHeight="1">
+      <c r="A276" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>الصناعة الغذائية / Industrie agroalimentaire</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>دخول الميناء / Accès au port</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>طلب تراخيص دخول للعمال المخولين للقيام بالأشغال على تجهيزات ميناء تال داخل الميناء / Demande d'autorisations d'accès pour les travailleurs habilités à intervenir sur les équipements portuaires à l'intérieur du port</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الدخول للميناء / Gestion des accès au port</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون / Salariés, fournisseurs</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، بطاقة ترقيم المركبة / Nom et prénom, date et lieu de naissance, n° CNI/permis de conduire/passeport, carte d'immatriculation du véhicule</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>03 أشهر / 3 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="190" customHeight="1">
+      <c r="A277" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المنتجات الغذائية / Production de produits alimentaires</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>الأرشفة القانونية والإدارية / Archivage juridique et administratif</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أرشفة الوثائق، الامتثال للالتزامات القانونية والتنظيمية، وتوفير المعلومات في حالة التفتيش أو التدقيق / Assurer l'archivage des documents, la conformité aux obligations légales et réglementaires et la mise à disposition des informations en cas d'inspection ou d'audit</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>الأرشفة القانونية والإدارية، تسيير العقود / Archivage juridique et administratif, gestion des contrats</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، المسيرون/الممثلون القانونيون للمؤسسة، الشركاء / Salariés, fournisseurs, clients actuels ou potentiels, dirigeants/représentants légaux de l'entreprise, partenaires</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الوظيفة، الدخل، الحساب البنكي، الكشوف البنكية، فاتورة، نسخ من العقود وسندات الطلبية والاتفاقات الداخلية، التصريحات الجبائية، التقارير المحاسبية، الوثائق المحاسبية (فواتير، كشوف، تصريح) / NIN, nom et prénom, date et lieu de naissance, situation familiale, adresse, e-mail, téléphone, n° CNI/permis de conduire/passeport, fonction, revenu, compte bancaire, relevés bancaires, facture, copies des contrats, bons de commande et conventions internes, déclarations fiscales, rapports comptables, documents comptables (factures, relevés, déclarations)</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="203" customHeight="1">
+      <c r="A278" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المنتجات الغذائية / Production de produits alimentaires</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>التسيير الإداري والمحاسبي والمالي / Gestion administrative, comptable et financière</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>لضمان التسيير الإداري والمحاسبي والمالي والتأمين للمنظم بما يتوافق مع الالتزامات القانونية والتنظيمية المعمول بها / Assurer la gestion administrative, comptable, financière et assurantielle de l'organisme conformément aux obligations légales et réglementaires en vigueur</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة، التسيير البنكي، تسيير الزبائن والموردين / Comptabilité, gestion bancaire, gestion des clients et fournisseurs</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، المسيرون/الممثلون القانونيون للمؤسسة، الشركاء، المتربصون، المتمهنون، المعالجون من الباطن / Salariés, fournisseurs, clients actuels ou potentiels, dirigeants/représentants légaux de l'entreprise, partenaires, stagiaires, apprentis, sous-traitants</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الحالة المهنية، رقم التسجيل الداخلي، المستخدم، رقم بطاقة الفلاح، رقم السجل التجاري، رقم بطاقة المقاول الذاتي، رقم التعريف الجبائي، الفواتير، المدفوعات، التحصيلات، رقم الحساب، كشف الهوية البنكية، رقم الحساب المصرفي الدولي، كشف التعاملات، العقود والاتفاقية / Nom et prénom, date et lieu de naissance, situation familiale, adresse, e-mail, téléphone, n° CNI/permis de conduire/passeport, statut professionnel, matricule interne, employeur, n° carte d'agriculteur, n° registre de commerce, n° carte d'auto-entrepreneur, NIF, factures, paiements, encaissements, n° de compte, RIB, IBAN, relevé des transactions, contrats et conventions</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="151" customHeight="1">
+      <c r="A279" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المنتجات الغذائية / Production de produits alimentaires</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة العامة / Comptabilité générale</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>لضمان الحفاظ على المحاسبة العامة، والامتثال للالتزامات القانونية والضريبية والمحاسبية، وإدارة العمليات المالية، وإعداد المستندات المحاسبية الإلزامية / Assurer la tenue de la comptabilité générale, la conformité aux obligations légales, fiscales et comptables, la gestion des opérations financières et l'établissement des documents comptables obligatoires</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة / Comptabilité</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، المسيرون، الممثلون القانونيون / Salariés, fournisseurs, clients actuels ou potentiels, dirigeants, représentants légaux</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم التعريف الوطني، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الوظيفة، المستخدم، كشف الهوية البنكية، بطاقة السحب المالي، الدخل، فواتير، مدفوعات، الكشوفات، الوثائق المالية، المراجع المحاسبية / Nom et prénom, date et lieu de naissance, situation familiale, photo, adresse, e-mail, téléphone, NIN, n° CNI/permis de conduire/passeport, fonction, employeur, RIB, carte de retrait, revenu, factures, paiements, relevés, documents financiers, références comptables</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="99" customHeight="1">
+      <c r="A280" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد / Importation</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، الحساب البنكي، رقم التعريف الجبائي، المادة الخاضعة للضريبة، رقم التعريف الإحصائي، رقم معرف شريك الأعمال / Nom et prénom, date et lieu de naissance, e-mail, téléphone, compte bancaire, NIF, article imposable, NIS, identifiant partenaire d'affaires</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>24 شهر / 24 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="99" customHeight="1">
+      <c r="A281" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد / Importation</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، الحساب البنكي، رقم التعريف الجبائي، المادة الخاضعة للضريبة، رقم التعريف الإحصائي، رقم معرف شريك الأعمال / Nom et prénom, date et lieu de naissance, e-mail, téléphone, compte bancaire, NIF, article imposable, NIS, identifiant partenaire d'affaires</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>24 شهر / 24 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="85" customHeight="1">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد / Importation</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الموظفين / Gestion des affaires du personnel</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الموظفين / Gestion des affaires du personnel</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، رقم التعريف الوطني، معطيات بيومترية، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، السيرة الذاتية، الحساب البنكي / Nom et prénom, date et lieu de naissance, e-mail, téléphone, NIN, données biométriques, n° pièce d'identité/permis de conduire/passeport, curriculum vitae, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>24 شهر / 24 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="85" customHeight="1">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>استيراد البذور الزيتية / Importation de graines oléagineuses</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>إدارة نظام المراقبة بالكاميرات / Gestion du système de surveillance par caméras</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>تأمين الدخول إلى المقرات / Sécurisation de l'accès aux locaux</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الزوار / Salariés, visiteurs</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>صورة / Photo</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>03 أشهر / 3 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="85" customHeight="1">
+      <c r="A284" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>استيراد معدات ومواد السباكة / Importation d'équipements et matériaux de plomberie</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، الحساب البنكي، رقم التعريف الجبائي، المادة الخاضعة للضريبة، رقم التعريف الإحصائي، رقم معرف شريك الأعمال / Nom et prénom, date et lieu de naissance, e-mail, téléphone, compte bancaire, NIF, article imposable, NIS, identifiant partenaire d'affaires</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>24 شهر (سنتان) / 24 mois (2 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="85" customHeight="1">
+      <c r="A285" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>استيراد معدات ومواد السباكة / Importation d'équipements et matériaux de plomberie</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، الحساب البنكي، رقم التعريف الجبائي، المادة الخاضعة للضريبة، رقم التعريف الإحصائي، رقم معرف شريك الأعمال / Nom et prénom, date et lieu de naissance, e-mail, téléphone, compte bancaire, NIF, article imposable, NIS, identifiant partenaire d'affaires</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>24 شهر (سنتان) / 24 mois (2 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="85" customHeight="1">
+      <c r="A286" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>الاستشارات والمساعدة في الاستثمار / Conseil et assistance en investissement</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>إدارة شؤون العاملين / Gestion des affaires du personnel</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>إدارة علاقات العمل وعقود العمل والمكافآت والتدريب والوظائف والمعاشات التقاعدية والتأمين والضمان الاجتماعي / Gestion des relations de travail, des contrats de travail, des rémunérations, de la formation, des emplois, des retraites, de l'assurance et de la sécurité sociale</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، رقم التعريف الوطني، الحالة العائلية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، صورة، السيرة الذاتية، الحساب البنكي / Nom et prénom, date et lieu de naissance, NIN, situation familiale, adresse de résidence, e-mail, téléphone, n° pièce d'identité/permis de conduire/passeport, photo, curriculum vitae, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="85" customHeight="1">
+      <c r="A287" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>الاستشارات والمساعدة في الاستثمار / Conseil et assistance en investissement</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>إدارة ملفات الزبائن / Gestion des dossiers clients</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>إدارة ملفات الزبائن المتعلقة بالموارد البشرية وعلاقات العمل / Gestion des dossiers clients relatifs aux ressources humaines et aux relations de travail</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، تاريخ ومكان الازدياد، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، عنوان السكن، الوظيفة، المستخدم، الحساب البنكي / Nom et prénom, téléphone, e-mail, date et lieu de naissance, n° pièce d'identité/permis de conduire/passeport, adresse de résidence, fonction, employeur, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="85" customHeight="1">
+      <c r="A288" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>الاستشارات والمساعدة في الاستثمار / Conseil et assistance en investissement</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الاستشاريين والمحامين / Gestion des consultants et avocats</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>إدارة ملفات الاستشاريين الخارجيين المتعلقة بالمشورة الاستثمارية وإدارة النزاعات / Gestion des dossiers des consultants externes relatifs au conseil en investissement et à la gestion des litiges</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الاستشاريين / Gestion des consultants</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>المحامون والاستشاريون / Avocats et consultants</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، صورة، رقم التعريف الوطني، عنوان السكن، الوظيفة، الحساب البنكي / Nom et prénom, date et lieu de naissance, e-mail, téléphone, n° pièce d'identité/permis de conduire/passeport, photo, NIN, adresse de résidence, fonction, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="85" customHeight="1">
+      <c r="A289" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>الدفع الإلكتروني / Paiement électronique</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>تسيير بيانات المستخدمين والمعاملات / Gestion des données des utilisateurs et des transactions</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>تسهيل المدفوعات بين التجار والزبائن، تسيير حسابات المستخدمين ومعاملاتهم، مكافحة الاحتيال وضمان الامتثال التنظيمي / Faciliter les paiements entre commerçants et clients, gérer les comptes et les transactions des utilisateurs, lutter contre la fraude et assurer la conformité réglementaire</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن، تسيير المستخدمين / Gestion des clients, gestion des utilisateurs</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، صورة، معطيات بيومترية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الحساب البنكي / Nom et prénom, date de naissance, photo, données biométriques, adresse de résidence, e-mail, téléphone, n° pièce d'identité/permis de conduire/passeport, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="85" customHeight="1">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>تركيب وصيانة العربات المحركة والهياكل الثابتة / Montage et maintenance de véhicules motorisés et de structures fixes</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>الأدلة القانونية للهيئات الاجتماعية / Registres légaux des organes sociaux</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>إدارة وتنسيق أنشطة الهيئات الاجتماعية وفق اللوائح / Gestion et coordination des activités des organes sociaux conformément à la réglementation</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>تسيير مسيري ومساهمي المؤسسة / Gestion des dirigeants et actionnaires de l'entreprise</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>المساهمون، الإداريون، المسيرون والمفوضون الاجتماعيون، الممثلون القانونيون / Actionnaires, administrateurs, dirigeants et mandataires sociaux, représentants légaux</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، رقم الهاتف، مستخرج من عقد الميلاد، عنوان البريد الإلكتروني، رقم الانتساب للضمان الاجتماعي، الوضعية المهنية / Nom et prénom, date et lieu de naissance, n° pièce d'identité/permis de conduire/passeport, téléphone, extrait d'acte de naissance, e-mail, n° d'affiliation à la sécurité sociale, situation professionnelle</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="85" customHeight="1">
+      <c r="A291" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>الصناعة الغذائية / Industrie agroalimentaire</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>الأحداث التسويقية والعروض الترويجية / Événements marketing et offres promotionnelles</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>جمع ومعالجة المعطيات في سياق المسابقات أو العروض الترويجية أو المبادرات / Collecte et traitement des données dans le cadre de concours, d'offres promotionnelles ou d'initiatives</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الفعاليات والعروض الترويجية / Gestion des événements et des offres promotionnelles</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، المتابعون على مواقع التواصل الاجتماعي / Salariés, abonnés sur les réseaux sociaux</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، عنوان السكن / Nom et prénom, e-mail, téléphone, adresse de résidence</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="85" customHeight="1">
+      <c r="A292" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>صناعة تجهيزات تصفية المياه / Fabrication d'équipements de traitement des eaux</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، الحساب البنكي، رقم التعريف الجبائي، المادة الخاضعة للضريبة، رقم التعريف الإحصائي، رقم معرف شريك الأعمال / Nom et prénom, date et lieu de naissance, e-mail, téléphone, compte bancaire, NIF, article imposable, NIS, identifiant partenaire d'affaires</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="85" customHeight="1">
+      <c r="A293" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>تصنيع الأدوية ذات الاستعمال البيطري / Fabrication de médicaments à usage vétérinaire</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزوار / Gestion des visiteurs</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>حماية الأشخاص والممتلكات / Protection des personnes et des biens</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزبائن الحاليون أو المحتملون، الزوار، المترشحون، الأجراء، المناولون، سائقو التوصيل / Fournisseurs, clients actuels ou potentiels, visiteurs, candidats, salariés, sous-traitants, chauffeurs-livreurs</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، نوع وترقيم المركبة / Nom et prénom, n° pièce d'identité/permis de conduire/passeport, type et immatriculation du véhicule</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="85" customHeight="1">
+      <c r="A294" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>التجارة الإلكترونية / Commerce électronique</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>تسيير موظفي المؤسسة / Gestion du personnel de l'entreprise</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>التسيير الإداري والمالي لموظفي المؤسسة، ملفات الموارد البشرية، الأجور، أوقات العمل، الالتزامات القانونية، التكوين، المسار المهني والأمن الداخلي / Gestion administrative et financière du personnel, dossiers des ressources humaines, salaires, temps de travail, obligations légales, formation, parcours professionnel et sécurité interne</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين، المحاسبة / Gestion du personnel, comptabilité</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، عنوان البريد الإلكتروني، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، معطيات بيومترية، الوظيفة، المستخدم، السيرة الذاتية، الحساب البنكي، الدخل / NIN, nom et prénom, date et lieu de naissance, situation familiale, photo, adresse de résidence, e-mail, n° pièce d'identité/permis de conduire/passeport, données biométriques, fonction, employeur, curriculum vitae, compte bancaire, revenu</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="85" customHeight="1">
+      <c r="A295" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>إدارة كاميرات المراقبة / Gestion des caméras de surveillance</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن الدخول إلى مقر الشركة / Assurer la sécurité de l'accès au siège de la société</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المراقبة عن طريق الفيديو / Gestion de la vidéosurveillance</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزوار، المترشحون / Salariés, fournisseurs, visiteurs, candidats</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>صورة / Photo</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>05 أشهر / 5 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="85" customHeight="1">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>إدارة التسليمات / Gestion des livraisons</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>تسليم البضائع / Livraison des marchandises</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التسليمات / Gestion des livraisons</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>سائقو مقدم خدمة النقل الطرقي للبضائع / Chauffeurs du prestataire de transport routier de marchandises (TRM)</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، رقم بطاقة الهوية / Nom et prénom, téléphone, n° carte d'identité</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="85" customHeight="1">
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>تركيب وصناعة المركبات الصناعية / Montage et fabrication de véhicules industriels</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>إدارة سجل الزوار / Gestion du registre des visiteurs</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>أمن الزوار والمصنع / Sécurité des visiteurs et de l'usine</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول، تسيير الزوار / Sécurité et contrôle des accès, gestion des visiteurs</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>الزوار / Visiteurs</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب / NIN, nom et prénom</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="85" customHeight="1">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>صناعة تجهيزات تصفية المياه / Fabrication d'équipements de traitement des eaux</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، الحساب البنكي، رقم التعريف الجبائي، المادة الخاضعة للضريبة، رقم التعريف الإحصائي، رقم معرف شريك الأعمال / Nom et prénom, date et lieu de naissance, e-mail, téléphone, compte bancaire, NIF, article imposable, NIS, identifiant partenaire d'affaires</t>
+        </is>
+      </c>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="85" customHeight="1">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>صناعة تجهيزات تصفية المياه / Fabrication d'équipements de traitement des eaux</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الموظفين / Gestion des affaires du personnel</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الموظفين / Gestion des affaires du personnel</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، رقم التعريف الوطني، معطيات بيومترية، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، السيرة الذاتية، الحساب البنكي / Nom et prénom, date et lieu de naissance, e-mail, téléphone, NIN, données biométriques, n° pièce d'identité/permis de conduire/passeport, curriculum vitae, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="85" customHeight="1">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج صناعي / Production industrielle</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التوظيف / Gestion du recrutement</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>الكفاءة في اختيار المترشحين / Efficacité dans la sélection des candidats</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المترشحين لمناصب شاغرة / Gestion des candidats aux postes vacants</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="inlineStr">
+        <is>
+          <t>المترشحون لمناصب شاغرة / Candidats aux postes vacants</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، الوظيفة، المستخدم، السيرة الذاتية، الدخل / Nom et prénom, date et lieu de naissance, situation familiale, adresse de résidence, e-mail, téléphone, fonction, employeur, curriculum vitae, revenu</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="85" customHeight="1">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج صناعي / Production industrielle</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين ومقدمي الخدمات / Gestion des fournisseurs et prestataires de services</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>تسيير العقود والطلبات والتواصل مع الموردين / Gestion des contrats, des commandes et de la communication avec les fournisseurs</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، الوظيفة، المستخدم / Nom et prénom, e-mail, téléphone, fonction, employeur</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="85" customHeight="1">
+      <c r="A302" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج صناعي / Production industrielle</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>تسيير العلاقات والتواصل مع الزبائن / Gestion des relations et de la communication avec les clients</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، الوظيفة، المستخدم / Nom et prénom, e-mail, téléphone, fonction, employeur</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="85" customHeight="1">
+      <c r="A303" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>الصناعة الصيدلانية / Industrie pharmaceutique</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>تسيير هيئات الإدارة / Gestion des organes d'administration</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>الامتثال للمتطلبات القانونية والتنظيمية / Conformité aux exigences légales et réglementaires</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الشركاء / Gestion des associés</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>الشركاء / Associés</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، عنوان السكن، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الوظيفة / NIN, nom et prénom, date et lieu de naissance, adresse de résidence, n° pièce d'identité/permis de conduire/passeport, fonction</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>240 شهر (20 سنة) / 240 mois (20 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="85" customHeight="1">
+      <c r="A304" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>تسيير العمال / Gestion des travailleurs</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموارد البشرية وكشوف الرواتب / Gestion des ressources humaines et des fiches de paie</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، صورة، الحالة العائلية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، بطاقة الشفاء، عقد الميلاد، بطاقة فصيلة الدم، ديبلوم وشهادة التكوين، صحيفة السوابق القضائية، التوقيع، بصمة لإثبات الحضور، السيرة الذاتية، الحساب البنكي، استمارة التعيين والتوظيف، الوضعية تجاه الخدمة الوطنية / Nom et prénom, date et lieu de naissance, photo, situation familiale, adresse de résidence, e-mail, téléphone, n° pièce d'identité/permis de conduire/passeport, carte Chifa, acte de naissance, carte de groupe sanguin, diplôme et attestation de formation, casier judiciaire, signature, empreinte de pointage, curriculum vitae, compte bancaire, formulaire de nomination et de recrutement, situation vis-à-vis du service national</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) لجميع المعطيات، و05 أشهر بالنسبة لصحيفة السوابق القضائية / 384 mois (32 ans) pour l'ensemble des données, et 5 mois pour le casier judiciaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="85" customHeight="1">
+      <c r="A305" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج منتجات النظافة الشخصية / Production de produits d'hygiène personnelle</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>تسيير مراقبة الدخول وأمن المواقع / Gestion du contrôle d'accès et de la sécurité des sites</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>أمن المواقع والممتلكات والأشخاص / Sécurité des sites, des biens et des personnes</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزبائن الحاليون أو المحتملون، الزوار / Fournisseurs, clients actuels ou potentiels, visiteurs</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، التوقيع، رقم تسجيل المركبة، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، المستخدم، اسم الشخص أو المصلحة المراد زيارتها / Nom et prénom, signature, numéro d'immatriculation du véhicule, n° pièce d'identité/permis de conduire/passeport, employeur, nom de la personne ou du service visité</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="85" customHeight="1">
+      <c r="A306" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>صناعة المنتجات الصيدلانية / Fabrication de produits pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الأمن الداخلي ومراقبة الدخول / Gestion de la sécurité interne et du contrôle d'accès</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الأمن الداخلي ومراقبة الدخول / Gestion de la sécurité interne et du contrôle d'accès</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزوار، المترشحون، المتمهنون، الزبائن الحاليون أو المحتملون / Fournisseurs, visiteurs, candidats, apprentis, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الوظيفة، المستخدم / Nom et prénom, n° pièce d'identité/permis de conduire/passeport, fonction, employeur</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="85" customHeight="1">
+      <c r="A307" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>صناعة المنتجات الصيدلانية / Fabrication de produits pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>إدارة نظام المعلومات والتكنولوجيا / Gestion du système d'information et de la technologie</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>ضمان تشغيل وأمن وفعالية الأنظمة المعلوماتية / Assurer le fonctionnement, la sécurité et l'efficacité des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الأنظمة المعلوماتية / Gestion des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان بروتوكول الأنترنت، الوظيفة، رقم الهاتف المهني، عنوان البريد الإلكتروني المهني / Nom et prénom, adresse IP, fonction, téléphone professionnel, e-mail professionnel</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="85" customHeight="1">
+      <c r="A308" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>الإدارة التجارية / Gestion commerciale</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>تطوير وإدارة الأنشطة التجارية / Développement et gestion des activités commerciales</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>التسيير التجاري / Gestion commerciale</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، رقم السجل التجاري، التوقيع، الوظيفة / Nom et prénom, adresse de résidence, téléphone, n° pièce d'identité/permis de conduire/passeport, n° registre de commerce, signature, fonction</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="85" customHeight="1">
+      <c r="A309" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>معطيات العمال / Données des travailleurs</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموارد البشرية وكشوف الرواتب / Gestion des ressources humaines et des fiches de paie</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، الديبلوم وشهادة التكوين، بصمة لإثبات الحضور، تاريخ ومكان الازدياد، صورة، عنوان السكن، رقم الهاتف، التوقيع، نسخة من بطاقة الشفاء، صحيفة السوابق القضائية، عقد الميلاد، بطاقة إقامة، شهادة عائلية، المستخدم، الوظيفة، الحساب البنكي، استمارة التعيين / Nom et prénom, diplôme et attestation de formation, empreinte de pointage, date et lieu de naissance, photo, adresse de résidence, téléphone, signature, copie de la carte Chifa, casier judiciaire, acte de naissance, carte de résidence, fiche familiale, employeur, fonction, compte bancaire, formulaire de nomination</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) لجميع المعطيات، و05 أشهر بالنسبة لصحيفة السوابق القضائية / 384 mois (32 ans) pour l'ensemble des données, et 5 mois pour le casier judiciaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="85" customHeight="1">
+      <c r="A310" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة وإدارة الخزينة / Comptabilité et gestion de la trésorerie</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>ضمان إدارة مالية فعالة من خلال مراقبة تدفقات الأموال / Assurer une gestion financière efficace par le contrôle des flux financiers</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة وإدارة الخزينة / Comptabilité et gestion de la trésorerie</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، عنوان السكن، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، نسخة من وثيقة الهوية الوطنية، التوقيع، رقم السجل التجاري، الحساب البنكي / Nom et prénom, e-mail, adresse de résidence, téléphone, n° pièce d'identité/permis de conduire/passeport, copie de la pièce d'identité nationale, signature, n° registre de commerce, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="85" customHeight="1">
+      <c r="A311" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المتمهنين / Gestion des apprentis</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>متابعة وتأطير تكوين المتمهنين / Suivi et encadrement de la formation des apprentis</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المتمهنين / Gestion des apprentis</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="inlineStr">
+        <is>
+          <t>المتمهنون / Apprentis</t>
+        </is>
+      </c>
+      <c r="G311" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، صورة، عنوان السكن، رقم الهاتف، نسخة من وثيقة الهوية الوطنية، التوقيع، اسم ولقب الوصي الشرعي، الحساب البنكي / Nom et prénom, date et lieu de naissance, photo, adresse de résidence, téléphone, copie de la pièce d'identité nationale, signature, nom et prénom du tuteur légal, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="inlineStr">
+        <is>
+          <t>36 شهر (03 سنوات) / 36 mois (3 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="85" customHeight="1">
+      <c r="A312" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>إدارة خدمة المستهلكين / Gestion du service consommateurs</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>إدارة تفاعلات المستهلكين لتحسين تجربة العملاء ودعم الأنشطة التسويقية / Gestion des interactions avec les consommateurs pour améliorer l'expérience client et soutenir les activités marketing</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>تسيير خدمة المستهلكين / Gestion du service consommateurs</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف / Nom et prénom, e-mail, téléphone</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="85" customHeight="1">
+      <c r="A313" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>إدارة معدات الحماية الفردية / Gestion des équipements de protection individuelle</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>توفير ومراقبة استخدام معدات الحماية الفردية / Fourniture et contrôle de l'utilisation des équipements de protection individuelle</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>تسيير معدات الحماية الفردية / Gestion des équipements de protection individuelle</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، التوقيع، الطول، مقاس الحذاء / Nom et prénom, signature, taille, pointure</t>
+        </is>
+      </c>
+      <c r="H313" s="3" t="inlineStr">
+        <is>
+          <t>24 شهر (سنتان) / 24 mois (2 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="85" customHeight="1">
+      <c r="A314" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>إدارة حملات الترويج والسحوبات / Gestion des campagnes promotionnelles et des tirages au sort</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>تخطيط وتنظيم وتنسيق الأنشطة التسويقية بهدف جذب انتباه العملاء / Planification, organisation et coordination des activités marketing en vue d'attirer l'attention des clients</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الترويج والسحوبات / Gestion des promotions et des tirages au sort</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، رقم الهاتف / Nom et prénom, adresse de résidence, téléphone</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="85" customHeight="1">
+      <c r="A315" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>لجنة التأديب / Commission de discipline</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>دراسة ومعالجة المخالفات التأديبية / Étude et traitement des infractions disciplinaires</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>اللجنة التأديبية / Commission disciplinaire</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، التوقيع، رقم الهاتف، عنوان السكن، الوظيفة / Nom et prénom, date de naissance, signature, téléphone, adresse de résidence, fonction</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="85" customHeight="1">
+      <c r="A316" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>توظيف واختيار المرشحين / Recrutement et sélection des candidats</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>استقطاب وتقييم وتوظيف المرشحين / Sourcing, évaluation et recrutement des candidats</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>التوظيف وانتقاء المترشحين / Recrutement et sélection des candidats</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>المترشحون / Candidats</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، عنوان البريد الإلكتروني، رقم الهاتف، السيرة الذاتية / Nom et prénom, date de naissance, e-mail, téléphone, curriculum vitae</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="85" customHeight="1">
+      <c r="A317" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>حماية الموقع / Protection du site</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن الموقع وممتلكات الشركة / Assurer la sécurité du site et des biens de la société</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزبائن الحاليون أو المحتملون، الزوار / Fournisseurs, clients actuels ou potentiels, visiteurs</t>
+        </is>
+      </c>
+      <c r="G317" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، نوع المركبة، ترقيم المركبة / Nom et prénom, n° pièce d'identité/permis de conduire/passeport, type de véhicule, immatriculation du véhicule</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="85" customHeight="1">
+      <c r="A318" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>المراقبة بالفيديو / Vidéosurveillance</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن الموقع وممتلكات الشركة / Assurer la sécurité du site et des biens de la société</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>المراقبة عن طريق الفيديو / Surveillance par vidéo</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، الزوار / Salariés, fournisseurs, clients actuels ou potentiels, visiteurs</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>صورة، فيديو، تسجيل صوتي / Photo, vidéo, enregistrement sonore</t>
+        </is>
+      </c>
+      <c r="H318" s="3" t="inlineStr">
+        <is>
+          <t>شهر واحد / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="85" customHeight="1">
+      <c r="A319" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>إدارة المراسلات الإلكترونية / Gestion des correspondances électroniques</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>ضمان توفر وأمن المراسلات الإلكترونية / Assurer la disponibilité et la sécurité des correspondances électroniques</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>تسيير البريد الإلكتروني / Gestion de la messagerie électronique</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، الوظيفة / Nom et prénom, e-mail, téléphone, fonction</t>
+        </is>
+      </c>
+      <c r="H319" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="85" customHeight="1">
+      <c r="A320" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>استشارة السوق / Consultation du marché</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>تحليل وتقييم عروض السوق / Analyse et évaluation des offres du marché</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>استشارة السوق / Consultation du marché</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، عنوان السكن، رقم السجل التجاري، التوقيع، الحساب البنكي / Nom et prénom, e-mail, téléphone, adresse de résidence, n° registre de commerce, signature, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H320" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="85" customHeight="1">
+      <c r="A321" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموردين وضمان جودة التوريدات وتوافقها واستمراريتها / Gestion des fournisseurs et garantie de la qualité, de la conformité et de la continuité des approvisionnements</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، التوقيع، رقم السجل التجاري، الحساب البنكي / Nom et prénom, adresse de résidence, e-mail, téléphone, n° pièce d'identité/permis de conduire/passeport, signature, n° registre de commerce, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H321" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="85" customHeight="1">
+      <c r="A322" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتسويق القهوة والمارغرين والطماطم المعلبة / Production et commercialisation de café, margarine et tomates en conserve</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>إدارة التسويق الميداني / Gestion du marketing terrain</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>تنفيذ الأنشطة التسويقية الميدانية / Mise en œuvre des activités marketing sur le terrain</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التسويق العملياتي / Gestion du marketing opérationnel</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G322" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، رقم الهاتف، التوقيع / Nom et prénom, adresse de résidence, téléphone, signature</t>
+        </is>
+      </c>
+      <c r="H322" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="85" customHeight="1">
+      <c r="A323" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>رقابة التسيير / Contrôle de gestion</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>رقابة الميزانية، متابعة أداء الأنشطة، إعداد التقارير، متابعة العمليات التجارية، ومتابعة وتحليل الأداء / Contrôle budgétaire, suivi de la performance des activités, élaboration des rapports, suivi des opérations commerciales, suivi et analyse de la performance</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>رقابة التسيير / Contrôle de gestion</t>
+        </is>
+      </c>
+      <c r="F323" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، مقدمو الخدمات / Salariés, fournisseurs, clients actuels ou potentiels, prestataires de services</t>
+        </is>
+      </c>
+      <c r="G323" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهيكل، نوع الخدمة، المبلغ / Nom et prénom, numéro de structure, type de prestation, montant</t>
+        </is>
+      </c>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="85" customHeight="1">
+      <c r="A324" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="inlineStr">
+        <is>
+          <t>تدقيق واعتماد الحسابات / Audit et certification des comptes</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>التحقق والتصديق على الحسابات / Vérification et certification des comptes</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>التدقيق واعتماد الحسابات / Audit et certification des comptes</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، الشركاء / Salariés, fournisseurs, clients actuels ou potentiels, associés</t>
+        </is>
+      </c>
+      <c r="G324" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عقد، اسم ولقب المسير، الوظيفة، كشف الهوية البنكية، صك، الدخل، فاتورة، المبلغ / Nom et prénom, contrat, nom et prénom du gérant, fonction, RIB, chèque, revenu, facture, montant</t>
+        </is>
+      </c>
+      <c r="H324" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="85" customHeight="1">
+      <c r="A325" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>التصريحات الضريبية / Déclarations fiscales</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>ضمان تقديم التصريحات الضريبية وتتبع التزامات الشركة / Assurer le dépôt des déclarations fiscales et le suivi des obligations de la société</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="inlineStr">
+        <is>
+          <t>التصاريح الجبائية / Déclarations fiscales</t>
+        </is>
+      </c>
+      <c r="F325" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، مقدمو الخدمات، الشركاء، محافظو الحسابات / Salariés, fournisseurs, clients actuels ou potentiels, prestataires de services, associés, commissaires aux comptes</t>
+        </is>
+      </c>
+      <c r="G325" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، رقم الضمان الاجتماعي، الحالة العائلية، عدد الأبناء، تاريخ ومكان الازدياد، رقم الهاتف، اسم ولقب الزوج(ة)، رقم المادة الخاضعة للضريبة، نوع الاتفاقية، رقم التعريف الجبائي، رقم السجل التجاري، رقم الاعتماد، طبيعة العمليات، رقم التعريف الإحصائي، المبلغ، مصدر الدخل، الدخل، الأجر الخاضع للضريبة، الضريبة على الدخل الإجمالي، تاريخ ومبلغ الاتفاقية، المبلغ المدفوع، طريقة الدفع / Nom et prénom, adresse de résidence, n° de sécurité sociale, situation familiale, nombre d'enfants, date et lieu de naissance, téléphone, nom et prénom du conjoint, n° d'article imposable, nature de la convention, NIF, n° registre de commerce, n° d'agrément, nature des opérations, NIS, montant, source du revenu, revenu, salaire imposable, IRG, date et montant de la convention, montant versé, mode de paiement</t>
+        </is>
+      </c>
+      <c r="H325" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="85" customHeight="1">
+      <c r="A326" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الشبكات والأنظمة / Gestion des réseaux et des systèmes</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>ضمان تأمين الشبكات والأنظمة / Assurer la sécurisation des réseaux et des systèmes</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>تسيير أمن الشبكات والأنظمة / Gestion de la sécurité des réseaux et des systèmes</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، مقدمو الخدمات / Salariés, prestataires de services</t>
+        </is>
+      </c>
+      <c r="G326" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني / Nom et prénom, téléphone, e-mail</t>
+        </is>
+      </c>
+      <c r="H326" s="3" t="inlineStr">
+        <is>
+          <t>180 شهر (15 سنة) / 180 mois (15 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="85" customHeight="1">
+      <c r="A327" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>تسيير تخزين البيانات / Gestion du stockage des données</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>تسيير تخزين بيانات المؤسسة / Gestion du stockage des données de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>تسيير تخزين البيانات / Gestion du stockage des données</t>
+        </is>
+      </c>
+      <c r="F327" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G327" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، عنوان السكن، تسجيل المكالمة، رقم التعريف الجبائي، رقم السجل التجاري / Nom et prénom, e-mail, téléphone, adresse de résidence, enregistrement d'appel, NIF, n° registre de commerce</t>
+        </is>
+      </c>
+      <c r="H327" s="3" t="inlineStr">
+        <is>
+          <t>180 شهر (15 سنة) / 180 mois (15 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="85" customHeight="1">
+      <c r="A328" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>تسيير العقود / Gestion des contrats</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>ضمان التسيير الإداري والقانوني للعقود / Assurer la gestion administrative et juridique des contrats</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>تسيير العقود / Gestion des contrats</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="inlineStr">
+        <is>
+          <t>مقدمو الخدمات للمؤسسة، الشركاء، المسير، الموردون، الزبائن الحاليون أو المحتملون / Prestataires de services de l'entreprise, associés, gérant, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G328" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان السكن، رقم الهاتف، عنوان البريد الإلكتروني، التوقيع، اسم ولقب المسير، منصب الموقّع، الوظيفة، رقم التعريف الجبائي، رقم التعريف الإحصائي / Nom et prénom, adresse de résidence, téléphone, e-mail, signature, nom et prénom du gérant, qualité du signataire, fonction, NIF, NIS</t>
+        </is>
+      </c>
+      <c r="H328" s="3" t="inlineStr">
+        <is>
+          <t>180 شهر (15 سنة) / 180 mois (15 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="85" customHeight="1">
+      <c r="A329" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>إدارة علاقات العملاء / Gestion de la relation client</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>الرد على طلبات الحصول على المعلومات من العملاء والمحتملين، وإدارة العلاقة مع العملاء، والرد على طلبات العملاء لشراء المنتجات وقطع الغيار، وتقديم الخدمات / Réponse aux demandes d'information des clients et prospects, gestion de la relation client, traitement des demandes d'achat de produits et de pièces de rechange, et fourniture des services</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F329" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G329" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، عنوان السكن، رقم التعريف الوطني، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، رقم الهاتف، بطاقة ترقيم المركبة، رقم التعريف الإحصائي، رقم التعريف الجبائي، رقم السجل التجاري، رقم المادة الخاضعة للضريبة / Nom et prénom, e-mail, adresse de résidence, NIN, n° pièce d'identité/permis de conduire/passeport, téléphone, carte d'immatriculation du véhicule, NIS, NIF, n° registre de commerce, n° d'article imposable</t>
+        </is>
+      </c>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>180 شهر (15 سنة) لجميع المعطيات، و480 شهر (40 سنة) بالنسبة لبطاقة ترقيم المركبة / 180 mois (15 ans) pour l'ensemble des données, et 480 mois (40 ans) pour la carte d'immatriculation du véhicule</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="85" customHeight="1">
+      <c r="A330" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="inlineStr">
+        <is>
+          <t>المساعدة التقنية / Assistance technique</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>حل المشاكل التقنية ومساعدة المستخدمين / Résolution des problèmes techniques et assistance aux utilisateurs</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الحوادث التقنية والرقمية / Gestion des incidents techniques et numériques</t>
+        </is>
+      </c>
+      <c r="F330" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G330" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، عنوان بروتوكول الأنترنت / Nom et prénom, e-mail, adresse IP</t>
+        </is>
+      </c>
+      <c r="H330" s="3" t="inlineStr">
+        <is>
+          <t>شهر واحد / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="85" customHeight="1">
+      <c r="A331" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>إدارة السجلات والتدوين / Gestion des journaux et de la journalisation</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>تتبع تسجيل الدخول ومراقبة الأنشطة / Traçabilité des connexions et surveillance des activités</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F331" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون / Salariés, fournisseurs</t>
+        </is>
+      </c>
+      <c r="G331" s="3" t="inlineStr">
+        <is>
+          <t>اسم المستخدم، عنوان بروتوكول الأنترنت، عنوان البريد الإلكتروني، عنوان التحكم في الوصول إلى الوسائط، الاسم واللقب / Nom d'utilisateur, adresse IP, e-mail, adresse MAC, nom et prénom</t>
+        </is>
+      </c>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="85" customHeight="1">
+      <c r="A332" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الولوج للمستخدمين / Gestion des accès des utilisateurs</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>إدارة وحماية الولوج إلى موارد تكنولوجيا المعلومات / Gestion et protection de l'accès aux ressources informatiques</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F332" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون / Salariés, fournisseurs</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، معرف التسجيل، الوظيفة / Nom et prénom, e-mail, identifiant de connexion, fonction</t>
+        </is>
+      </c>
+      <c r="H332" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="85" customHeight="1">
+      <c r="A333" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>الاستيراد لإعادة البيع على الحالة / Importation pour revente en l'état</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الدخول والأمن / Gestion des accès et de la sécurité</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>تأمين العمال والزوار وممتلكات الشركة / Sécurisation des travailleurs, des visiteurs et des biens de la société</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F333" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، شارة الأجير، بطاقة ترقيم المركبة / NIN, nom et prénom, n° pièce d'identité/permis de conduire/passeport, badge du salarié, carte d'immatriculation du véhicule</t>
+        </is>
+      </c>
+      <c r="H333" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="85" customHeight="1">
+      <c r="A334" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>صناعة اللافتات الإشهارية / Fabrication d'enseignes publicitaires</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>المراقبة بالفيديو / Vidéosurveillance</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>ضمان أمن الأشخاص والممتلكات والمباني، والوقاية من أعمال التخريب أو السرقة أو الإتلاف، والتحكم في الدخول إلى الفضاءات المهنية / Assurer la sécurité des personnes, des biens et des bâtiments, prévenir les actes de vandalisme, de vol ou de dégradation, et contrôler l'accès aux espaces professionnels</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>الأمن ومراقبة الدخول / Sécurité et contrôle des accès</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون، الأشخاص الأجانب / Salariés, fournisseurs, clients actuels ou potentiels, personnes étrangères</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>صورة / Photo</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="inlineStr">
+        <is>
+          <t>شهر واحد / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="85" customHeight="1">
+      <c r="A335" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>صناعة اللافتات الإشهارية / Fabrication d'enseignes publicitaires</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>ضمان التسيير الإداري والمحاسبي والتعاقدي للعلاقات مع الموردين / Assurer la gestion administrative, comptable et contractuelle des relations avec les fournisseurs</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F335" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، الوظيفة، المستخدم، الحساب البنكي / Nom et prénom, fonction, employeur, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) بالنسبة للاسم واللقب والوظيفة والمستخدم، و120 شهر (10 سنوات) بالنسبة للحساب البنكي / 60 mois (5 ans) pour le nom et prénom, la fonction et l'employeur, et 120 mois (10 ans) pour le compte bancaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="85" customHeight="1">
+      <c r="A336" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>صناعة اللافتات الإشهارية / Fabrication d'enseignes publicitaires</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الموظفين والأجور / Gestion des affaires du personnel et des salaires</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>ضمان إدارة شؤون الموظفين والأجور / Assurer la gestion des affaires du personnel et des salaires</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F336" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ الازدياد، الحالة العائلية، عنوان السكن، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، رقم التعريف الوطني، السيرة الذاتية، شهادات العمل، الشهادات / Nom et prénom, date de naissance, situation familiale, adresse de résidence, n° pièce d'identité/permis de conduire/passeport, NIN, curriculum vitae, certificats de travail, diplômes</t>
+        </is>
+      </c>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>03 أشهر بالنسبة للاسم واللقب وتاريخ الازدياد والحالة العائلية وعنوان السكن ورقم وثيقة الهوية/رخصة السياقة/جواز السفر، وشهرين بالنسبة للسيرة الذاتية، و01 شهر بالنسبة لرقم التعريف الوطني وشهادات العمل والشهادات / 3 mois pour le nom et prénom, la date de naissance, la situation familiale, l'adresse et la pièce d'identité/permis/passeport, 2 mois pour le curriculum vitae, et 1 mois pour le NIN, les certificats de travail et les diplômes</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="85" customHeight="1">
+      <c r="A337" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>صناعة اللافتات الإشهارية / Fabrication d'enseignes publicitaires</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التسويق / Gestion du marketing</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>تسيير النشاط التجاري للمؤسسة، بما في ذلك متابعة المبيعات والعروض والطلبيات والتسليم والفوترة والدفع / Gestion de l'activité commerciale de l'entreprise, y compris le suivi des ventes, des offres, des commandes, de la livraison, de la facturation et du paiement</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F337" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، الوظيفة، المستخدم، الحساب البنكي / Nom et prénom, e-mail, téléphone, fonction, employeur, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="85" customHeight="1">
+      <c r="A338" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المواد الصيدلانية / Production de matières pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>إدارة طلبات التوظيف / Gestion des demandes de recrutement</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>التوظيف لحساب بيوجينال / Recrutement pour le compte de Biogenal</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المترشحين / Gestion des candidats</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>المترشحون / Candidats</t>
+        </is>
+      </c>
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، السيرة الذاتية، الوظيفة / Nom et prénom, date et lieu de naissance, adresse de résidence, e-mail, téléphone, curriculum vitae, fonction</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="85" customHeight="1">
+      <c r="A339" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المواد الصيدلانية / Production de matières pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الترويج الطبي والصيدلاني / Gestion de la promotion médicale et pharmaceutique</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>ترقية منتجات بيوجينال / Promotion des produits Biogenal</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الترويج والبيع / Gestion de la promotion et de la vente</t>
+        </is>
+      </c>
+      <c r="F339" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم الهاتف، عنوان البريد الإلكتروني، نسخة من بطاقة الهوية، رقم السجل التجاري، رقم التعريف الجبائي، القانون الأساسي للمؤسسة، بطاقة أعمال / Nom et prénom, téléphone, e-mail, copie de la pièce d'identité, n° registre de commerce, NIF, statuts de l'entreprise, carte de visite</t>
+        </is>
+      </c>
+      <c r="H339" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="85" customHeight="1">
+      <c r="A340" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المواد الصيدلانية / Production de matières pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="inlineStr">
+        <is>
+          <t>إدارة اليقظة الدوائية والمعلومات الطبية وشكاوى الجودة / Gestion de la pharmacovigilance, de l'information médicale et des réclamations qualité</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>رصد وتقييم والوقاية من مخاطر الآثار الضارة المرتبطة باستخدام الأدوية والمستلزمات الطبية وإدارتها / Détection, évaluation, prévention et gestion des risques d'effets indésirables liés à l'utilisation des médicaments et dispositifs médicaux</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>تسيير اليقظة الدوائية والمعلومات الطبية وشكاوى الجودة / Gestion de la pharmacovigilance, de l'information médicale et des réclamations qualité</t>
+        </is>
+      </c>
+      <c r="F340" s="3" t="inlineStr">
+        <is>
+          <t>المصرّحون (الصيادلة، الأطباء، المرضى) / Déclarants (pharmaciens, médecins, patients)</t>
+        </is>
+      </c>
+      <c r="G340" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، صورة، تاريخ الازدياد، مستخرج من عقد الميلاد، الجنس، أثر جانبي غير مرغوب فيه، الشهادة، التخصص / Nom et prénom, photo, date de naissance, extrait d'acte de naissance, sexe, effet indésirable, diplôme, spécialité</t>
+        </is>
+      </c>
+      <c r="H340" s="3" t="inlineStr">
+        <is>
+          <t>240 شهر (20 سنة) / 240 mois (20 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="85" customHeight="1">
+      <c r="A341" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المواد الصيدلانية / Production de matières pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الأمن الداخلي ومراقبة الدخول / Gestion de la sécurité interne et du contrôle d'accès</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الأمن الداخلي ومراقبة الدخول / Gestion de la sécurité interne et du contrôle d'accès</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الأمن الداخلي ومراقبة الدخول / Gestion de la sécurité interne et du contrôle d'accès</t>
+        </is>
+      </c>
+      <c r="F341" s="3" t="inlineStr">
+        <is>
+          <t>الموردون، الزبائن الحاليون أو المحتملون، الزوار / Fournisseurs, clients actuels ou potentiels, visiteurs</t>
+        </is>
+      </c>
+      <c r="G341" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، صورة، الترقيم / Nom et prénom, n° pièce d'identité/permis de conduire/passeport, photo, immatriculation</t>
+        </is>
+      </c>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="85" customHeight="1">
+      <c r="A342" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المواد الصيدلانية / Production de matières pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>تسيير موردي بيوجينال / Gestion des fournisseurs de Biogenal</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F342" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G342" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، رقم التعريف الجبائي، التسمية الاجتماعية، الحساب البنكي / Nom et prénom, e-mail, téléphone, NIF, dénomination sociale, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="85" customHeight="1">
+      <c r="A343" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج المواد الصيدلانية / Production de matières pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>إدارة نظم المعلومات / Gestion des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>إدارة نظم المعلومات في شركة بيوجينال / Gestion des systèmes d'information au sein de la société Biogenal</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>تسيير نظم المعلومات / Gestion des systèmes d'information</t>
+        </is>
+      </c>
+      <c r="F343" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G343" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، صورة، معطيات بيومترية / Nom et prénom, photo, données biométriques</t>
+        </is>
+      </c>
+      <c r="H343" s="3" t="inlineStr">
+        <is>
+          <t>504 أشهر (42 سنة) / 504 mois (42 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="85" customHeight="1">
+      <c r="A344" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>رقمنة الشركات / Digitalisation des entreprises</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموارد البشرية / Gestion des ressources humaines</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>إدارة وتسيير المستخدمين، التدريب، الرواتب، والامتثال للالتزامات القانونية والتعاقدية طبقًا لمقتضيات قانون العمل / Administration et gestion du personnel, formation, salaires et conformité aux obligations légales et contractuelles conformément au code du travail</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G344" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، مستخرج من عقد الميلاد، الحالة العائلية، صورة، عنوان السكن، عنوان البريد الإلكتروني، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، اسم ولقب ذوي الحقوق، رقم الضمان الاجتماعي، رقم التعريف الوطني، معطيات بيومترية، الوظيفة، الحساب البنكي / Nom et prénom, date et lieu de naissance, extrait d'acte de naissance, situation familiale, photo, adresse de résidence, e-mail, n° pièce d'identité/permis de conduire/passeport, nom et prénom des ayants droit, n° de sécurité sociale, NIN, données biométriques, fonction, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H344" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="85" customHeight="1">
+      <c r="A345" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>رقمنة الشركات / Digitalisation des entreprises</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المتربصين / Gestion des stagiaires</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>ضمان التسيير الإداري واللوجستي للمتربصين، وكذا تقييم كفاءاتهم / Assurer la gestion administrative et logistique des stagiaires ainsi que l'évaluation de leurs compétences</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المتربصين / Gestion des stagiaires</t>
+        </is>
+      </c>
+      <c r="F345" s="3" t="inlineStr">
+        <is>
+          <t>المتربصون / Stagiaires</t>
+        </is>
+      </c>
+      <c r="G345" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، صورة، عنوان السكن، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الإقامة / NIN, nom et prénom, date et lieu de naissance, photo, adresse de résidence, téléphone, n° pièce d'identité/permis de conduire/passeport, résidence</t>
+        </is>
+      </c>
+      <c r="H345" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="85" customHeight="1">
+      <c r="A346" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>رقمنة الشركات / Digitalisation des entreprises</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المشتريات (التوريد) / Gestion des achats (approvisionnement)</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>إدارة العلاقات مع الموردين، بما في ذلك اختيارهم والتفاوض معهم ومتابعة عقود الشراء، بالإضافة إلى إدارة المدفوعات / Gestion des relations avec les fournisseurs, y compris leur sélection, la négociation, le suivi des contrats d'achat et la gestion des paiements</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الموردين / Gestion des fournisseurs</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="inlineStr">
+        <is>
+          <t>الموردون / Fournisseurs</t>
+        </is>
+      </c>
+      <c r="G346" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، رقم الهاتف، الفاكس، الوظيفة، عنوان المقر الاجتماعي، التسمية الاجتماعية، رقم السجل التجاري، النشاط، رقم التعريف الإحصائي، رقم التعريف الجبائي، رقم المادة الخاضعة للضريبة، رقم الاعتماد، كشف الهوية البنكية/كشف الهوية البريدية، رقم الحساب المصرفي الدولي/رقم الحساب / Nom et prénom, e-mail, téléphone, fax, fonction, adresse du siège social, dénomination sociale, n° registre de commerce, activité, NIS, NIF, n° d'article imposable, n° d'agrément, RIB/RIP, IBAN/n° de compte</t>
+        </is>
+      </c>
+      <c r="H346" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="85" customHeight="1">
+      <c r="A347" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>رقمنة الشركات / Digitalisation des entreprises</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>إدارة المبيعات - الزبائن / Gestion des ventes - clients</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>إدارة المعاملات التجارية من الفوترة إلى تحصيل الديون وتسوية المنازعات التجارية / Gestion des transactions commerciales, de la facturation au recouvrement des créances et au règlement des litiges commerciaux</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الزبائن / Gestion des clients</t>
+        </is>
+      </c>
+      <c r="F347" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G347" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان البريد الإلكتروني، عنوان البريد الإلكتروني المهني، رقم الهاتف، الفاكس، النشاط، رقم التعريف الجبائي، رقم المادة الخاضعة للضريبة، رقم التعريف الإحصائي، الوظيفة، المستخدم، رقم التسجيل أو رمز (الموظف، الزبون)، عنوان المقر الاجتماعي، التسمية الاجتماعية، رقم السجل التجاري، رقم الاعتماد، كشف الهوية البنكية/كشف الهوية البريدية، رقم الحساب المصرفي الدولي/رقم الحساب / Nom et prénom, e-mail, e-mail professionnel, téléphone, fax, activité, NIF, n° d'article imposable, NIS, fonction, employeur, numéro ou code d'enregistrement (employé, client), adresse du siège social, dénomination sociale, n° registre de commerce, n° d'agrément, RIB/RIP, IBAN/n° de compte</t>
+        </is>
+      </c>
+      <c r="H347" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="85" customHeight="1">
+      <c r="A348" s="2" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>رقمنة الشركات / Digitalisation des entreprises</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التشغيل / Gestion du recrutement</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>تقييم قدرات المرشحين واختيار الأكثر كفاءة / Évaluation des aptitudes des candidats et sélection des plus compétents</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التوظيف / Gestion du recrutement</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="inlineStr">
+        <is>
+          <t>المترشحون / Candidats</t>
+        </is>
+      </c>
+      <c r="G348" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، الوضعية تجاه الخدمة الوطنية، المستوى الدراسي، الجنسية، السيرة الذاتية، الشهادات / Nom et prénom, date et lieu de naissance, situation familiale, photo, adresse de résidence, e-mail, téléphone, situation vis-à-vis du service national, niveau d'études, nationalité, curriculum vitae, diplômes</t>
+        </is>
+      </c>
+      <c r="H348" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="85" customHeight="1">
+      <c r="A349" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتصنيع المنتجات الصيدلانية / Production et fabrication de produits pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>الموارد البشرية / Ressources humaines</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>التسيير الإداري للمستخدمين / Gestion administrative du personnel</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F349" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G349" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، بطاقة الخدمة الوطنية، رقم الضمان الاجتماعي، الديبلومات والشهادات، صحيفة السوابق القضائية، السيرة الذاتية، شهادة العمل، الوظيفة، الرقم التعريفي للعامل، الحساب البنكي / Nom et prénom, date et lieu de naissance, situation familiale, photo, adresse de résidence, e-mail, téléphone, n° pièce d'identité/permis de conduire/passeport, carte du service national, n° de sécurité sociale, diplômes et attestations, casier judiciaire, curriculum vitae, certificat de travail, fonction, matricule du travailleur, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H349" s="3" t="inlineStr">
+        <is>
+          <t>480 شهر (40 سنة) لجميع المعطيات، و05 أشهر بالنسبة لصحيفة السوابق القضائية / 480 mois (40 ans) pour l'ensemble des données, et 5 mois pour le casier judiciaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="85" customHeight="1">
+      <c r="A350" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتصنيع المنتجات الصيدلانية / Production et fabrication de produits pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>إدارة حضور العمال / Gestion de la présence des travailleurs</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>رصد ومراقبة وتسجيل حضور العمال / Suivi, contrôle et enregistrement de la présence des travailleurs</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F350" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G350" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، بصمة الأصبع، معطيات بيومترية، صورة، الوظيفة / Nom et prénom, empreinte digitale, données biométriques, photo, fonction</t>
+        </is>
+      </c>
+      <c r="H350" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="85" customHeight="1">
+      <c r="A351" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتصنيع المنتجات الصيدلانية / Production et fabrication de produits pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>طب العمل / Médecine du travail</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>طب العمل / Médecine du travail</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين، تسيير طب العمل / Gestion du personnel, gestion de la médecine du travail</t>
+        </is>
+      </c>
+      <c r="F351" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G351" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، زمرة الدم، الوظيفة / Nom et prénom, date et lieu de naissance, situation familiale, groupe sanguin, fonction</t>
+        </is>
+      </c>
+      <c r="H351" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="85" customHeight="1">
+      <c r="A352" s="2" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتصنيع المنتجات الصيدلانية / Production et fabrication de produits pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C352" s="3" t="inlineStr">
+        <is>
+          <t>الرواتب والمنح الخاصة بالعمال والتكاليف والمصاريف الملحقة بالرواتب / Salaires, primes des travailleurs, charges et frais annexes aux salaires</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>محاسبة ودفع الرواتب والمنح الخاصة بالعمال / Comptabilisation et paiement des salaires et des primes des travailleurs</t>
+        </is>
+      </c>
+      <c r="E352" s="3" t="inlineStr">
+        <is>
+          <t>المحاسبة، تسيير الأجور / Comptabilité, gestion des salaires</t>
+        </is>
+      </c>
+      <c r="F352" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G352" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، الدخل، الحساب البنكي / Nom et prénom, revenu, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H352" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="85" customHeight="1">
+      <c r="A353" s="2" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج وتصنيع المنتجات الصيدلانية / Production et fabrication de produits pharmaceutiques</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t>إدارة التوظيف / Gestion du recrutement</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>تقييم المهارات، التواصل مع المرشحين، التحقق من المراجع والمطابقة القانونية / Évaluation des compétences, communication avec les candidats, vérification des références et conformité légale</t>
+        </is>
+      </c>
+      <c r="E353" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المترشحين / Gestion des candidats</t>
+        </is>
+      </c>
+      <c r="F353" s="3" t="inlineStr">
+        <is>
+          <t>المترشحون المحتملون / Candidats potentiels</t>
+        </is>
+      </c>
+      <c r="G353" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، الوظيفة، المستخدم، السيرة الذاتية / Nom et prénom, date et lieu de naissance, situation familiale, photo, adresse de résidence, e-mail, téléphone, fonction, employeur, curriculum vitae</t>
+        </is>
+      </c>
+      <c r="H353" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="85" customHeight="1">
+      <c r="A354" s="2" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج السلع / Production de biens</t>
+        </is>
+      </c>
+      <c r="C354" s="3" t="inlineStr">
+        <is>
+          <t>معالجة التصريحات الجبائية / Traitement des déclarations fiscales</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>ضمان إعداد وتقديم التصريحات الجبائية الإلزامية للمؤسسة، ومتابعة الالتزامات القانونية تجاه الإدارة الجبائية / Assurer l'établissement et le dépôt des déclarations fiscales obligatoires de l'entreprise, et le suivi des obligations légales envers l'administration fiscale</t>
+        </is>
+      </c>
+      <c r="E354" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التصريحات الجبائية / Gestion des déclarations fiscales</t>
+        </is>
+      </c>
+      <c r="F354" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G354" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، الوظيفة، المستخدم، معلومات قانونية وجبائية، رقم الضمان الاجتماعي، الدخل / Nom et prénom, fonction, employeur, informations juridiques et fiscales, n° de sécurité sociale, revenu</t>
+        </is>
+      </c>
+      <c r="H354" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="85" customHeight="1">
+      <c r="A355" s="2" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج السلع / Production de biens</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الملفات الإدارية للموظفين وإعداد عقود العمل / Gestion des dossiers administratifs des employés et établissement des contrats de travail</t>
+        </is>
+      </c>
+      <c r="E355" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F355" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G355" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، عنوان البريد الإلكتروني، رقم وثيقة الهوية/رخصة السياقة/جواز السفر / NIN, nom et prénom, date et lieu de naissance, situation familiale, photo, adresse de résidence, e-mail, n° pièce d'identité/permis de conduire/passeport</t>
+        </is>
+      </c>
+      <c r="H355" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="85" customHeight="1">
+      <c r="A356" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج السلع / Production de biens</t>
+        </is>
+      </c>
+      <c r="C356" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الأرشيف الإداري / Gestion des archives administratives</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>الاحتفاظ بالوثائق الإدارية وتنظيمها وإدارتها لضمان توفرها وتتبعها والامتثال للقوانين / Conservation, organisation et gestion des documents administratifs afin d'assurer leur disponibilité, leur traçabilité et la conformité aux lois</t>
+        </is>
+      </c>
+      <c r="E356" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الأرشيف الإداري / Gestion des archives administratives</t>
+        </is>
+      </c>
+      <c r="F356" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء، الموردون، الزبائن الحاليون أو المحتملون / Salariés, fournisseurs, clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G356" s="3" t="inlineStr">
+        <is>
+          <t>معلومات قانونية وجبائية حول الزبائن والموردين، الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، عنوان البريد الإلكتروني، رقم الهاتف، المستخدم / Informations juridiques et fiscales relatives aux clients et fournisseurs, nom et prénom, date et lieu de naissance, situation familiale, adresse de résidence, e-mail, téléphone, employeur</t>
+        </is>
+      </c>
+      <c r="H356" s="3" t="inlineStr">
+        <is>
+          <t>120 شهر (10 سنوات) / 120 mois (10 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="85" customHeight="1">
+      <c r="A357" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>إنتاج السلع / Production de biens</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التكوين / Gestion de la formation</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>ضمان تخطيط ومتابعة وتطوير مهارات الموظفين والمتربصين في التكوين المهني بهدف تحسين أدائهم وكفاءتهم داخل المؤسسة / Assurer la planification, le suivi et le développement des compétences des employés et des stagiaires en formation professionnelle afin d'améliorer leur performance et leur efficacité au sein de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E357" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F357" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G357" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، عنوان السكن، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، نسخة من الشهادة / NIN, nom et prénom, date et lieu de naissance, situation familiale, adresse de résidence, n° pièce d'identité/permis de conduire/passeport, copie du diplôme</t>
+        </is>
+      </c>
+      <c r="H357" s="3" t="inlineStr">
+        <is>
+          <t>60 شهر (05 سنوات) / 60 mois (5 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="85" customHeight="1">
+      <c r="A358" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>صناعة العجائن الغذائية والكسكسي / Fabrication de pâtes alimentaires et de couscous</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="inlineStr">
+        <is>
+          <t>إدارة تكوين الموظفين / Gestion de la formation des employés</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>ضمان تكوين الموظفين / Assurer la formation des employés</t>
+        </is>
+      </c>
+      <c r="E358" s="3" t="inlineStr">
+        <is>
+          <t>تسيير تكوين الموظفين / Gestion de la formation des employés</t>
+        </is>
+      </c>
+      <c r="F358" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G358" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الوظيفة / Nom et prénom, date et lieu de naissance, fonction</t>
+        </is>
+      </c>
+      <c r="H358" s="3" t="inlineStr">
+        <is>
+          <t>384 شهر (32 سنة) / 384 mois (32 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="85" customHeight="1">
+      <c r="A359" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>صناعة العجائن الغذائية والكسكسي / Fabrication de pâtes alimentaires et de couscous</t>
+        </is>
+      </c>
+      <c r="C359" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الصيانة / Gestion de la maintenance</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>ضمان الصيانة التقنية لمعدات مطحنة عمور / Assurer la maintenance technique des équipements de la semoulerie Amour</t>
+        </is>
+      </c>
+      <c r="E359" s="3" t="inlineStr">
+        <is>
+          <t>تسيير الصيانة / Gestion de la maintenance</t>
+        </is>
+      </c>
+      <c r="F359" s="3" t="inlineStr">
+        <is>
+          <t>أعوان الصيانة الخارجية / Agents de maintenance externes</t>
+        </is>
+      </c>
+      <c r="G359" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، التوقيع / Nom et prénom, signature</t>
+        </is>
+      </c>
+      <c r="H359" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="85" customHeight="1">
+      <c r="A360" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>صناعة العجائن الغذائية والكسكسي / Fabrication de pâtes alimentaires et de couscous</t>
+        </is>
+      </c>
+      <c r="C360" s="3" t="inlineStr">
+        <is>
+          <t>إدارة الاتصال والتسويق / Gestion de la communication et du marketing</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>الترويج لخدمات مطحنة عمور / Promotion des services de la semoulerie Amour</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="inlineStr">
+        <is>
+          <t>تسيير التواصل والتسويق / Gestion de la communication et du marketing</t>
+        </is>
+      </c>
+      <c r="F360" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G360" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، صور، رقم الهاتف / Nom et prénom, photos, téléphone</t>
+        </is>
+      </c>
+      <c r="H360" s="3" t="inlineStr">
+        <is>
+          <t>شهر واحد / 1 mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="85" customHeight="1">
+      <c r="A361" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>البلاستيك والمطاط / Plastique et caoutchouc</t>
+        </is>
+      </c>
+      <c r="C361" s="3" t="inlineStr">
+        <is>
+          <t>المعلومات الشخصية للعمال / Informations personnelles des travailleurs</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>تسيير شؤون المستخدمين والأجور / Gestion des affaires du personnel et des salaires</t>
+        </is>
+      </c>
+      <c r="E361" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F361" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G361" s="3" t="inlineStr">
+        <is>
+          <t>رقم التعريف الوطني، الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، عنوان السكن، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الشهادة أو المستوى الدراسي، شهادة طبية، السيرة الذاتية، الحساب البنكي / NIN, nom et prénom, date et lieu de naissance, situation familiale, photo, adresse de résidence, n° pièce d'identité/permis de conduire/passeport, diplôme ou niveau d'études, certificat médical, curriculum vitae, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H361" s="3" t="inlineStr">
+        <is>
+          <t>504 أشهر (42 سنة) / 504 mois (42 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="85" customHeight="1">
+      <c r="A362" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>تحويل البلاستيك / Transformation du plastique</t>
+        </is>
+      </c>
+      <c r="C362" s="3" t="inlineStr">
+        <is>
+          <t>المعلومات الشخصية للعمال / Informations personnelles des travailleurs</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>تسيير شؤون المستخدمين والأجور / Gestion des affaires du personnel et des salaires</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="inlineStr">
+        <is>
+          <t>تسيير المستخدمين / Gestion du personnel</t>
+        </is>
+      </c>
+      <c r="F362" s="3" t="inlineStr">
+        <is>
+          <t>الأجراء / Salariés</t>
+        </is>
+      </c>
+      <c r="G362" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، تاريخ ومكان الازدياد، الحالة العائلية، صورة، معطيات بيومترية، عنوان السكن، رقم وثيقة الهوية/رخصة السياقة/جواز السفر، الشهادة أو المستوى الدراسي، شهادة طبية، السيرة الذاتية، الحساب البنكي / Nom et prénom, date et lieu de naissance, situation familiale, photo, données biométriques, adresse de résidence, n° pièce d'identité/permis de conduire/passeport, diplôme ou niveau d'études, certificat médical, curriculum vitae, compte bancaire</t>
+        </is>
+      </c>
+      <c r="H362" s="3" t="inlineStr">
+        <is>
+          <t>504 أشهر (42 سنة) / 504 mois (42 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="85" customHeight="1">
+      <c r="A363" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>برمجة أنظمة الإعلام الآلي / Programmation de systèmes informatiques</t>
+        </is>
+      </c>
+      <c r="C363" s="3" t="inlineStr">
+        <is>
+          <t>استضافة ووضع تطبيق ويب لتسيير الخدمات الصحية / Hébergement et mise en place d'une application web pour la gestion des services de santé</t>
+        </is>
+      </c>
+      <c r="D363" s="3" t="inlineStr">
+        <is>
+          <t>توفير واستضافة وصيانة تطبيق ويب لتسيير الخدمات الصحية في الجزائر، مع حصر الوصول إلى المعطيات في الدعم التقني فقط وبناءً على طلب العميل / Fourniture, hébergement et maintenance d'une application web de gestion des services de santé en Algérie, l'accès aux données étant limité au support technique et uniquement à la demande du client</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="inlineStr">
+        <is>
+          <t>وضع واستضافة وصيانة تقنية لتطبيق ويب لتسيير الخدمات الصحية من قبل المؤسسات الصحية / Mise en place, hébergement et maintenance technique d'une application web de gestion des services de santé pour les établissements de santé</t>
+        </is>
+      </c>
+      <c r="F363" s="3" t="inlineStr">
+        <is>
+          <t>الزبائن الحاليون أو المحتملون / Clients actuels ou potentiels</t>
+        </is>
+      </c>
+      <c r="G363" s="3" t="inlineStr">
+        <is>
+          <t>الاسم واللقب، عنوان العيادة أو المصلحة، التوقيع / Nom et prénom, adresse du cabinet ou du service, signature</t>
+        </is>
+      </c>
+      <c r="H363" s="3" t="inlineStr">
+        <is>
+          <t>12 شهر / 12 mois</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H363"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
